--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_3.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_3.xlsx
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[2, 7, 4, 5, 9]</t>
+          <t>[4, 6, 2, 8, 9]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -472,70 +472,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9553939325706483</v>
+        <v>0.951554812292568</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9553939325706483</v>
+        <v>0.951554812292568</v>
       </c>
       <c r="E2" t="n">
-        <v>87.86</v>
+        <v>85.66</v>
       </c>
       <c r="F2" t="n">
-        <v>69.47</v>
+        <v>74.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[7, 4, 5, 4, 7]</t>
+          <t>[4, 3, 3, 6, 5]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 3, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9540352176415541</v>
+        <v>0.9807471216376641</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9540352176415541</v>
+        <v>0.9807471216376641</v>
       </c>
       <c r="E3" t="n">
-        <v>90.84999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>76.98</v>
+        <v>79.03</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[2, 6, 9, 5, 8]</t>
+          <t>[2, 4, 9, 5, 3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9478403060903626</v>
+        <v>0.9603978087993985</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9478403060903626</v>
+        <v>0.9603978087993985</v>
       </c>
       <c r="E4" t="n">
-        <v>85.84999999999999</v>
+        <v>91.89999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>71.77000000000001</v>
+        <v>79.05999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[2, 1, 4, 7, 3]</t>
+          <t>[0, 0, 6, 4, 2]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -544,46 +544,46 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9623638426515638</v>
+        <v>0.9666862085457614</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9623638426515638</v>
+        <v>0.9666862085457614</v>
       </c>
       <c r="E5" t="n">
-        <v>92.58999999999999</v>
+        <v>75.36</v>
       </c>
       <c r="F5" t="n">
-        <v>63.6</v>
+        <v>79.87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[3, 0, 7, 7, 2]</t>
+          <t>[3, 8, 3, 4, 2]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9564991064089393</v>
+        <v>0.9727416048827108</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9564991064089393</v>
+        <v>0.9727416048827108</v>
       </c>
       <c r="E6" t="n">
-        <v>91.38</v>
+        <v>89.16</v>
       </c>
       <c r="F6" t="n">
-        <v>65.16000000000001</v>
+        <v>76.75999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[1, 8, 8, 0, 0]</t>
+          <t>[9, 9, 0, 6, 8]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -592,70 +592,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9574855509406018</v>
+        <v>0.9480576739204637</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9574855509406018</v>
+        <v>0.9480576739204637</v>
       </c>
       <c r="E7" t="n">
-        <v>93.56999999999999</v>
+        <v>86.41999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>72.97</v>
+        <v>73.23999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[3, 2, 3, 1, 5]</t>
+          <t>[3, 0, 0, 5, 3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9693868973916436</v>
+        <v>0.9731495283948514</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9693868973916436</v>
+        <v>0.9731495283948514</v>
       </c>
       <c r="E8" t="n">
-        <v>97.11999999999999</v>
+        <v>82.52</v>
       </c>
       <c r="F8" t="n">
-        <v>60.11</v>
+        <v>74.44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[9, 2, 3, 2, 4]</t>
+          <t>[2, 7, 4, 5, 3]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9594597500105426</v>
+        <v>0.9611425337994506</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9594597500105426</v>
+        <v>0.9611425337994506</v>
       </c>
       <c r="E9" t="n">
-        <v>85.22999999999999</v>
+        <v>92.87</v>
       </c>
       <c r="F9" t="n">
-        <v>64.45999999999999</v>
+        <v>77.69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[7, 9, 5, 9, 3]</t>
+          <t>[7, 2, 9, 9, 6]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -664,70 +664,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9325269865690435</v>
+        <v>0.945440170336321</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9325269865690435</v>
+        <v>0.945440170336321</v>
       </c>
       <c r="E10" t="n">
-        <v>97.14999999999999</v>
+        <v>92.03</v>
       </c>
       <c r="F10" t="n">
-        <v>61.75</v>
+        <v>74.56</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[1, 9, 7, 2, 9]</t>
+          <t>[3, 0, 8, 3, 5]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9508501566036863</v>
+        <v>0.9671508636147387</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9508501566036863</v>
+        <v>0.9671508636147387</v>
       </c>
       <c r="E11" t="n">
-        <v>91.88</v>
+        <v>90.8</v>
       </c>
       <c r="F11" t="n">
-        <v>56.21</v>
+        <v>72.05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[2, 2, 6, 1, 1]</t>
+          <t>[8, 4, 3, 1, 3]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9776000579520334</v>
+        <v>0.961070904065761</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9776000579520334</v>
+        <v>0.961070904065761</v>
       </c>
       <c r="E12" t="n">
-        <v>99.05</v>
+        <v>81.64</v>
       </c>
       <c r="F12" t="n">
-        <v>72.20999999999999</v>
+        <v>64.20999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[0, 4, 7, 0, 8]</t>
+          <t>[9, 1, 8, 9, 6]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -736,22 +736,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9615636971775878</v>
+        <v>0.9442696767587364</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9615636971775878</v>
+        <v>0.9442696767587364</v>
       </c>
       <c r="E13" t="n">
-        <v>89.05999999999999</v>
+        <v>97.02000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>78.11</v>
+        <v>71.95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[4, 7, 9, 6, 3]</t>
+          <t>[0, 6, 5, 9, 9]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -760,46 +760,46 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9409838440339965</v>
+        <v>0.9522688951016044</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9409838440339965</v>
+        <v>0.9522688951016044</v>
       </c>
       <c r="E14" t="n">
-        <v>90.41</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>69.63</v>
+        <v>70.58</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[3, 6, 1, 8, 8]</t>
+          <t>[3, 3, 0, 8, 9]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9521829349593633</v>
+        <v>0.9819676350506552</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9521829349593633</v>
+        <v>0.9819676350506552</v>
       </c>
       <c r="E15" t="n">
-        <v>95.83</v>
+        <v>89.92000000000002</v>
       </c>
       <c r="F15" t="n">
-        <v>69.78999999999999</v>
+        <v>75.25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[0, 6, 7, 9, 3]</t>
+          <t>[8, 0, 1, 1, 5]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -808,46 +808,46 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9434440568581082</v>
+        <v>0.9653062929828313</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9434440568581082</v>
+        <v>0.9653062929828313</v>
       </c>
       <c r="E16" t="n">
-        <v>90.67999999999999</v>
+        <v>95.98</v>
       </c>
       <c r="F16" t="n">
-        <v>67.59999999999999</v>
+        <v>72.22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[5, 7, 9, 2, 6]</t>
+          <t>[3, 5, 6, 9, 4]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9466642227051313</v>
+        <v>0.9748224804069322</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9466642227051313</v>
+        <v>0.9748224804069322</v>
       </c>
       <c r="E17" t="n">
-        <v>85.71000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="F17" t="n">
-        <v>68.53999999999999</v>
+        <v>74.88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[1, 5, 1, 2, 1]</t>
+          <t>[0, 9, 9, 7, 8]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -856,22 +856,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9685873594146293</v>
+        <v>0.9472631566511484</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9685873594146293</v>
+        <v>0.9472631566511484</v>
       </c>
       <c r="E18" t="n">
-        <v>95.95999999999999</v>
+        <v>87.91</v>
       </c>
       <c r="F18" t="n">
-        <v>55.98999999999999</v>
+        <v>73.81</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[2, 0, 3, 2, 5]</t>
+          <t>[8, 9, 4, 6, 4]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -880,22 +880,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9703113924911201</v>
+        <v>0.9437866648651491</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9703113924911201</v>
+        <v>0.9437866648651491</v>
       </c>
       <c r="E19" t="n">
-        <v>85.84999999999999</v>
+        <v>80.12</v>
       </c>
       <c r="F19" t="n">
-        <v>67.31999999999999</v>
+        <v>71.86999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[8, 3, 6, 6, 3]</t>
+          <t>[6, 1, 2, 0, 4]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -904,22 +904,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9465311257571133</v>
+        <v>0.9665354979550512</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9465311257571133</v>
+        <v>0.9665354979550512</v>
       </c>
       <c r="E20" t="n">
-        <v>91.22999999999999</v>
+        <v>85.96000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>72.47</v>
+        <v>78.58</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[3, 0, 3, 9, 8]</t>
+          <t>[9, 7, 8, 1, 5]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9585874483605946</v>
+        <v>0.9466294320778831</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9585874483605946</v>
+        <v>0.9466294320778831</v>
       </c>
       <c r="E21" t="n">
-        <v>97.92</v>
+        <v>96.39</v>
       </c>
       <c r="F21" t="n">
-        <v>65.45</v>
+        <v>68.44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[6, 2, 9, 4, 2]</t>
+          <t>[5, 8, 5, 6, 0]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -952,22 +952,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9484248084189454</v>
+        <v>0.9500044122188814</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9484248084189454</v>
+        <v>0.9500044122188814</v>
       </c>
       <c r="E22" t="n">
-        <v>78.13</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>69.84</v>
+        <v>65.08</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[9, 7, 5, 5, 6]</t>
+          <t>[5, 2, 8, 7, 0]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -976,22 +976,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9426299072724829</v>
+        <v>0.9542751390927819</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9426299072724829</v>
+        <v>0.9542751390927819</v>
       </c>
       <c r="E23" t="n">
-        <v>90.39999999999999</v>
+        <v>85.66999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>72.02</v>
+        <v>72.84999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[4, 2, 5, 8, 3]</t>
+          <t>[6, 1, 2, 9, 6]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1000,22 +1000,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9586352396291958</v>
+        <v>0.9563884919503243</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9586352396291958</v>
+        <v>0.9563884919503243</v>
       </c>
       <c r="E24" t="n">
-        <v>90.83</v>
+        <v>96.12</v>
       </c>
       <c r="F24" t="n">
-        <v>73.24000000000001</v>
+        <v>74.55000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[1, 0, 5, 3, 6]</t>
+          <t>[3, 4, 8, 1, 0]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1024,22 +1024,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9669076677967297</v>
+        <v>0.9613622477395609</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9669076677967297</v>
+        <v>0.9613622477395609</v>
       </c>
       <c r="E25" t="n">
-        <v>92.51000000000001</v>
+        <v>81.74000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>68.90000000000001</v>
+        <v>71.02</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[7, 4, 1, 3, 0]</t>
+          <t>[6, 0, 4, 4, 9]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1048,46 +1048,46 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9618064071696564</v>
+        <v>0.9592744650379746</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9618064071696564</v>
+        <v>0.9592744650379746</v>
       </c>
       <c r="E26" t="n">
-        <v>95.07999999999998</v>
+        <v>74.84</v>
       </c>
       <c r="F26" t="n">
-        <v>67.00999999999999</v>
+        <v>75.14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[2, 7, 7, 0, 2]</t>
+          <t>[6, 4, 3, 6, 1]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9604349194719223</v>
+        <v>0.955663288620604</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9604349194719223</v>
+        <v>0.955663288620604</v>
       </c>
       <c r="E27" t="n">
-        <v>98.50999999999999</v>
+        <v>85.46000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>78.29000000000001</v>
+        <v>66.70999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[2, 8, 6, 9, 1]</t>
+          <t>[7, 9, 5, 8, 1]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1096,22 +1096,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9426766843112941</v>
+        <v>0.9432429520821359</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9426766843112941</v>
+        <v>0.9432429520821359</v>
       </c>
       <c r="E28" t="n">
-        <v>87.75</v>
+        <v>96.39</v>
       </c>
       <c r="F28" t="n">
-        <v>65.36</v>
+        <v>68.44</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[7, 6, 3, 2, 7]</t>
+          <t>[1, 6, 6, 9, 3]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1120,94 +1120,94 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.954761568880224</v>
+        <v>0.9496597678045416</v>
       </c>
       <c r="D29" t="n">
-        <v>0.954761568880224</v>
+        <v>0.9496597678045416</v>
       </c>
       <c r="E29" t="n">
-        <v>88.95999999999999</v>
+        <v>91.12</v>
       </c>
       <c r="F29" t="n">
-        <v>66.25999999999999</v>
+        <v>66.47</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[6, 0, 5, 0, 5]</t>
+          <t>[3, 5, 2, 3, 3]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9604858011766972</v>
+        <v>0.9695614010075723</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9604858011766972</v>
+        <v>0.9695614010075723</v>
       </c>
       <c r="E30" t="n">
-        <v>85.92999999999999</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>79.59</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[7, 4, 4, 9, 9]</t>
+          <t>[4, 6, 3, 2, 5]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9449610124196149</v>
+        <v>0.9648714732704561</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9449610124196149</v>
+        <v>0.9648714732704561</v>
       </c>
       <c r="E31" t="n">
-        <v>89.73</v>
+        <v>94.38</v>
       </c>
       <c r="F31" t="n">
-        <v>70.02</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[0, 8, 0, 5, 5]</t>
+          <t>[3, 9, 0, 6, 7]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9597411037043432</v>
+        <v>0.967383584372226</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9597411037043432</v>
+        <v>0.967383584372226</v>
       </c>
       <c r="E32" t="n">
-        <v>91.11</v>
+        <v>95.23</v>
       </c>
       <c r="F32" t="n">
-        <v>78.97</v>
+        <v>78.32000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[5, 3, 5, 8, 1]</t>
+          <t>[3, 9, 4, 9, 5]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1216,22 +1216,22 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9563707740534437</v>
+        <v>0.9485424429234302</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9563707740534437</v>
+        <v>0.9485424429234302</v>
       </c>
       <c r="E33" t="n">
-        <v>99.88999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="F33" t="n">
-        <v>68.35000000000001</v>
+        <v>65.95</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[0, 3, 7, 3, 9]</t>
+          <t>[8, 7, 7, 9, 4]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1240,166 +1240,166 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9609604579978079</v>
+        <v>0.9382105752039229</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9609604579978079</v>
+        <v>0.9382105752039229</v>
       </c>
       <c r="E34" t="n">
-        <v>97.78</v>
+        <v>88.24000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>62.22000000000001</v>
+        <v>70.83</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[1, 8, 2, 4, 0]</t>
+          <t>[3, 8, 4, 5, 3]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9616235092112209</v>
+        <v>0.9778527649486021</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9616235092112209</v>
+        <v>0.9778527649486021</v>
       </c>
       <c r="E35" t="n">
-        <v>88.04999999999998</v>
+        <v>90.16</v>
       </c>
       <c r="F35" t="n">
-        <v>71.11</v>
+        <v>70.44</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[9, 7, 2, 6, 2]</t>
+          <t>[1, 3, 5, 7, 0]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9480375216938952</v>
+        <v>0.9620170166859339</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9480375216938952</v>
+        <v>0.9620170166859339</v>
       </c>
       <c r="E36" t="n">
-        <v>95.31999999999999</v>
+        <v>85.99000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>77.31999999999999</v>
+        <v>66.75</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[5, 5, 6, 4, 9]</t>
+          <t>[5, 3, 6, 6, 6]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9526038142807739</v>
+        <v>0.9720291710644789</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9526038142807739</v>
+        <v>0.9720291710644789</v>
       </c>
       <c r="E37" t="n">
-        <v>87.50999999999999</v>
+        <v>96.12</v>
       </c>
       <c r="F37" t="n">
-        <v>76.8</v>
+        <v>69.88</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[2, 2, 7, 0, 1]</t>
+          <t>[2, 6, 1, 3, 2]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9826438871703432</v>
+        <v>0.9649783310809342</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9826438871703432</v>
+        <v>0.9649783310809342</v>
       </c>
       <c r="E38" t="n">
-        <v>99.98999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>74.7</v>
+        <v>74.65000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[6, 2, 1, 6, 9]</t>
+          <t>[9, 7, 8, 9, 9]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9734714370151635</v>
+        <v>0.9344195387987428</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9734714370151635</v>
+        <v>0.9344195387987428</v>
       </c>
       <c r="E39" t="n">
-        <v>96.87</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>78.23999999999999</v>
+        <v>71.96000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[2, 0, 9, 2, 2]</t>
+          <t>[9, 3, 3, 6, 5]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9614246189600537</v>
+        <v>0.9748183304877425</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9614246189600537</v>
+        <v>0.9748183304877425</v>
       </c>
       <c r="E40" t="n">
-        <v>78.33</v>
+        <v>92.03999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>63.3</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[3, 2, 3, 7, 2]</t>
+          <t>[0, 7, 6, 9, 9]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1408,22 +1408,22 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9625267852124515</v>
+        <v>0.9490832742370341</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9625267852124515</v>
+        <v>0.9490832742370341</v>
       </c>
       <c r="E41" t="n">
-        <v>90.94999999999999</v>
+        <v>87.13</v>
       </c>
       <c r="F41" t="n">
-        <v>60.22</v>
+        <v>73.29000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[4, 0, 4, 1, 3]</t>
+          <t>[0, 8, 3, 0, 4]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1432,22 +1432,22 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9678172626828864</v>
+        <v>0.9669064281415869</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9678172626828864</v>
+        <v>0.9669064281415869</v>
       </c>
       <c r="E42" t="n">
-        <v>92.19</v>
+        <v>71.14</v>
       </c>
       <c r="F42" t="n">
-        <v>71.78999999999999</v>
+        <v>72.31</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[1, 6, 7, 5, 1]</t>
+          <t>[4, 7, 9, 0, 8]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1456,94 +1456,94 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9533497280024732</v>
+        <v>0.9537152189022599</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9533497280024732</v>
+        <v>0.9537152189022599</v>
       </c>
       <c r="E43" t="n">
-        <v>94.55</v>
+        <v>82.25</v>
       </c>
       <c r="F43" t="n">
-        <v>64.09</v>
+        <v>74.05</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[4, 7, 8, 1, 2]</t>
+          <t>[9, 5, 7, 3, 5]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9542548378487707</v>
+        <v>0.9660013085719255</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9542548378487707</v>
+        <v>0.9660013085719255</v>
       </c>
       <c r="E44" t="n">
-        <v>90.67</v>
+        <v>99.53</v>
       </c>
       <c r="F44" t="n">
-        <v>68.36</v>
+        <v>71.13</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[4, 3, 0, 5, 2]</t>
+          <t>[0, 3, 3, 0, 5]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9659299230803022</v>
+        <v>0.9752016263835088</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9659299230803022</v>
+        <v>0.9752016263835088</v>
       </c>
       <c r="E45" t="n">
-        <v>88.06999999999999</v>
+        <v>85.52</v>
       </c>
       <c r="F45" t="n">
-        <v>72.76000000000001</v>
+        <v>75.31999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[2, 9, 2, 7, 5]</t>
+          <t>[3, 1, 9, 0, 6]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9613650950589684</v>
+        <v>0.9633889275079145</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9613650950589684</v>
+        <v>0.9633889275079145</v>
       </c>
       <c r="E46" t="n">
-        <v>99.94</v>
+        <v>86.62</v>
       </c>
       <c r="F46" t="n">
-        <v>76.28999999999999</v>
+        <v>70.26000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[4, 1, 1, 8, 5]</t>
+          <t>[7, 5, 5, 5, 4]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1552,46 +1552,46 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.9619680649016652</v>
+        <v>0.9537520314562707</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9619680649016652</v>
+        <v>0.9537520314562707</v>
       </c>
       <c r="E47" t="n">
-        <v>96.83999999999999</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>68.25</v>
+        <v>61.38</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[1, 2, 4, 2, 7]</t>
+          <t>[5, 3, 7, 8, 5]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9682857955990112</v>
+        <v>0.9565544296694727</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9682857955990112</v>
+        <v>0.9565544296694727</v>
       </c>
       <c r="E48" t="n">
-        <v>85.41999999999999</v>
+        <v>99.78999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>64.47</v>
+        <v>69.70999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[4, 5, 4, 7, 7]</t>
+          <t>[5, 2, 3, 2, 6]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1600,22 +1600,22 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.9540352176415541</v>
+        <v>0.966504712008936</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9540352176415541</v>
+        <v>0.966504712008936</v>
       </c>
       <c r="E49" t="n">
-        <v>90.84999999999999</v>
+        <v>83.69999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>76.98</v>
+        <v>70.01000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[9, 3, 3, 9, 0]</t>
+          <t>[5, 7, 2, 7, 4]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.9482684987543984</v>
+        <v>0.953038153871152</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9482684987543984</v>
+        <v>0.953038153871152</v>
       </c>
       <c r="E50" t="n">
-        <v>97.00999999999999</v>
+        <v>85.74000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>60.15000000000001</v>
+        <v>71.28999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[0, 1, 7, 5, 5]</t>
+          <t>[4, 7, 1, 9, 1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1648,16 +1648,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.9612304266396028</v>
+        <v>0.9521242789993772</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9612304266396028</v>
+        <v>0.9521242789993772</v>
       </c>
       <c r="E51" t="n">
-        <v>95.06999999999999</v>
+        <v>98.17</v>
       </c>
       <c r="F51" t="n">
-        <v>69.40000000000001</v>
+        <v>74.74000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_3.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_3.xlsx
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[4, 6, 2, 8, 9]</t>
+          <t>[8, 8, 3, 8, 3]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -472,190 +472,190 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.951554812292568</v>
+        <v>0.9523548174993759</v>
       </c>
       <c r="D2" t="n">
-        <v>0.951554812292568</v>
+        <v>0.9523548174993759</v>
       </c>
       <c r="E2" t="n">
-        <v>85.66</v>
+        <v>71.78999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>74.75</v>
+        <v>52.78000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[4, 3, 3, 6, 5]</t>
+          <t>[9, 6, 1, 6, 8]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[1, 3, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9807471216376641</v>
+        <v>0.9748122188995546</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9807471216376641</v>
+        <v>0.9748122188995546</v>
       </c>
       <c r="E3" t="n">
-        <v>99.59999999999999</v>
+        <v>90.72</v>
       </c>
       <c r="F3" t="n">
-        <v>79.03</v>
+        <v>73.18000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[2, 4, 9, 5, 3]</t>
+          <t>[2, 5, 5, 3, 1]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9603978087993985</v>
+        <v>0.9784457206442835</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9603978087993985</v>
+        <v>0.9784457206442835</v>
       </c>
       <c r="E4" t="n">
-        <v>91.89999999999999</v>
+        <v>96.24000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>79.05999999999999</v>
+        <v>74.03</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[0, 0, 6, 4, 2]</t>
+          <t>[6, 8, 5, 3, 5]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9666862085457614</v>
+        <v>0.991346541033757</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9666862085457614</v>
+        <v>0.991346541033757</v>
       </c>
       <c r="E5" t="n">
-        <v>75.36</v>
+        <v>97.22</v>
       </c>
       <c r="F5" t="n">
-        <v>79.87</v>
+        <v>78.31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[3, 8, 3, 4, 2]</t>
+          <t>[0, 5, 6, 7, 1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9727416048827108</v>
+        <v>0.9623043882032117</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9727416048827108</v>
+        <v>0.9623043882032117</v>
       </c>
       <c r="E6" t="n">
-        <v>89.16</v>
+        <v>85.47</v>
       </c>
       <c r="F6" t="n">
-        <v>76.75999999999999</v>
+        <v>75.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[9, 9, 0, 6, 8]</t>
+          <t>[5, 7, 8, 5, 8]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9480576739204637</v>
+        <v>0.9751773529514862</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9480576739204637</v>
+        <v>0.9751773529514862</v>
       </c>
       <c r="E7" t="n">
-        <v>86.41999999999999</v>
+        <v>96.40000000000002</v>
       </c>
       <c r="F7" t="n">
-        <v>73.23999999999999</v>
+        <v>76.34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[3, 0, 0, 5, 3]</t>
+          <t>[2, 9, 5, 5, 0]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9731495283948514</v>
+        <v>0.9767725249917432</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9731495283948514</v>
+        <v>0.9767725249917432</v>
       </c>
       <c r="E8" t="n">
-        <v>82.52</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>74.44</v>
+        <v>77.82000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[2, 7, 4, 5, 3]</t>
+          <t>[5, 6, 6, 0, 1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9611425337994506</v>
+        <v>0.9749148737824358</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9611425337994506</v>
+        <v>0.9749148737824358</v>
       </c>
       <c r="E9" t="n">
-        <v>92.87</v>
+        <v>82.56</v>
       </c>
       <c r="F9" t="n">
-        <v>77.69</v>
+        <v>74.78</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[7, 2, 9, 9, 6]</t>
+          <t>[4, 7, 5, 0, 5]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -664,70 +664,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.945440170336321</v>
+        <v>0.9616764806447367</v>
       </c>
       <c r="D10" t="n">
-        <v>0.945440170336321</v>
+        <v>0.9616764806447367</v>
       </c>
       <c r="E10" t="n">
-        <v>92.03</v>
+        <v>73.94</v>
       </c>
       <c r="F10" t="n">
-        <v>74.56</v>
+        <v>69.09</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[3, 0, 8, 3, 5]</t>
+          <t>[6, 3, 3, 1, 6]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9671508636147387</v>
+        <v>0.9811741550728131</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9671508636147387</v>
+        <v>0.9811741550728131</v>
       </c>
       <c r="E11" t="n">
-        <v>90.8</v>
+        <v>87.27</v>
       </c>
       <c r="F11" t="n">
-        <v>72.05</v>
+        <v>73.83000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[8, 4, 3, 1, 3]</t>
+          <t>[3, 3, 8, 2, 6]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.961070904065761</v>
+        <v>0.9652236619239314</v>
       </c>
       <c r="D12" t="n">
-        <v>0.961070904065761</v>
+        <v>0.9652236619239314</v>
       </c>
       <c r="E12" t="n">
-        <v>81.64</v>
+        <v>92.74000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>64.20999999999999</v>
+        <v>75.66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[9, 1, 8, 9, 6]</t>
+          <t>[1, 0, 1, 7, 5]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -736,502 +736,502 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9442696767587364</v>
+        <v>0.9673570125253914</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9442696767587364</v>
+        <v>0.9673570125253914</v>
       </c>
       <c r="E13" t="n">
-        <v>97.02000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="F13" t="n">
-        <v>71.95</v>
+        <v>62.79</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[0, 6, 5, 9, 9]</t>
+          <t>[8, 9, 6, 0, 0]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9522688951016044</v>
+        <v>0.9746387001203755</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9522688951016044</v>
+        <v>0.9746387001203755</v>
       </c>
       <c r="E14" t="n">
-        <v>84.04000000000001</v>
+        <v>87.70000000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>70.58</v>
+        <v>73.23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[3, 3, 0, 8, 9]</t>
+          <t>[9, 9, 8, 5, 6]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9819676350506552</v>
+        <v>0.943512371817541</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9819676350506552</v>
+        <v>0.943512371817541</v>
       </c>
       <c r="E15" t="n">
-        <v>89.92000000000002</v>
+        <v>82.31000000000002</v>
       </c>
       <c r="F15" t="n">
-        <v>75.25</v>
+        <v>62.11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[8, 0, 1, 1, 5]</t>
+          <t>[5, 3, 5, 8, 5]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9653062929828313</v>
+        <v>0.9770775842779535</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9653062929828313</v>
+        <v>0.9770775842779535</v>
       </c>
       <c r="E16" t="n">
-        <v>95.98</v>
+        <v>97.42</v>
       </c>
       <c r="F16" t="n">
-        <v>72.22</v>
+        <v>78.87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[3, 5, 6, 9, 4]</t>
+          <t>[3, 9, 2, 0, 3]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9748224804069322</v>
+        <v>0.9628934893227344</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9748224804069322</v>
+        <v>0.9628934893227344</v>
       </c>
       <c r="E17" t="n">
-        <v>94.5</v>
+        <v>85.91</v>
       </c>
       <c r="F17" t="n">
-        <v>74.88</v>
+        <v>68.28999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[0, 9, 9, 7, 8]</t>
+          <t>[7, 5, 4, 6, 8]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9472631566511484</v>
+        <v>0.9750886966351833</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9472631566511484</v>
+        <v>0.9750886966351833</v>
       </c>
       <c r="E18" t="n">
-        <v>87.91</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>73.81</v>
+        <v>77.69</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[8, 9, 4, 6, 4]</t>
+          <t>[5, 6, 5, 5, 0]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9437866648651491</v>
+        <v>0.9740383454531771</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9437866648651491</v>
+        <v>0.9740383454531771</v>
       </c>
       <c r="E19" t="n">
-        <v>80.12</v>
+        <v>80.34</v>
       </c>
       <c r="F19" t="n">
-        <v>71.86999999999999</v>
+        <v>73.91</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[6, 1, 2, 0, 4]</t>
+          <t>[5, 8, 5, 5, 6]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 2, 1]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9665354979550512</v>
+        <v>0.9930050318088361</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9665354979550512</v>
+        <v>0.9930050318088361</v>
       </c>
       <c r="E20" t="n">
-        <v>85.96000000000001</v>
+        <v>95.77000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>78.58</v>
+        <v>79.44999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[9, 7, 8, 1, 5]</t>
+          <t>[8, 6, 2, 3, 9]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9466294320778831</v>
+        <v>0.9755744197481937</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9466294320778831</v>
+        <v>0.9755744197481937</v>
       </c>
       <c r="E21" t="n">
-        <v>96.39</v>
+        <v>98.61</v>
       </c>
       <c r="F21" t="n">
-        <v>68.44</v>
+        <v>77.47000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[5, 8, 5, 6, 0]</t>
+          <t>[6, 5, 2, 5, 1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9500044122188814</v>
+        <v>0.9619311515094581</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9500044122188814</v>
+        <v>0.9619311515094581</v>
       </c>
       <c r="E22" t="n">
-        <v>82.18000000000001</v>
+        <v>96.24000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>65.08</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[5, 2, 8, 7, 0]</t>
+          <t>[3, 0, 5, 8, 0]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9542751390927819</v>
+        <v>0.9786324543950282</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9542751390927819</v>
+        <v>0.9786324543950282</v>
       </c>
       <c r="E23" t="n">
-        <v>85.66999999999999</v>
+        <v>83.14</v>
       </c>
       <c r="F23" t="n">
-        <v>72.84999999999999</v>
+        <v>72.93000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[6, 1, 2, 9, 6]</t>
+          <t>[1, 0, 6, 6, 6]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9563884919503243</v>
+        <v>0.9790507664171814</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9563884919503243</v>
+        <v>0.9790507664171814</v>
       </c>
       <c r="E24" t="n">
-        <v>96.12</v>
+        <v>82.02</v>
       </c>
       <c r="F24" t="n">
-        <v>74.55000000000001</v>
+        <v>76.31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[3, 4, 8, 1, 0]</t>
+          <t>[6, 6, 6, 9, 8]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9613622477395609</v>
+        <v>0.9713479034623994</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9613622477395609</v>
+        <v>0.9713479034623994</v>
       </c>
       <c r="E25" t="n">
-        <v>81.74000000000001</v>
+        <v>94.94</v>
       </c>
       <c r="F25" t="n">
-        <v>71.02</v>
+        <v>76.60000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[6, 0, 4, 4, 9]</t>
+          <t>[4, 5, 6, 5, 3]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9592744650379746</v>
+        <v>0.9765463076207255</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9592744650379746</v>
+        <v>0.9765463076207255</v>
       </c>
       <c r="E26" t="n">
-        <v>74.84</v>
+        <v>89.99000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>75.14</v>
+        <v>76.03999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[6, 4, 3, 6, 1]</t>
+          <t>[3, 8, 0, 5, 3]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.955663288620604</v>
+        <v>0.9803172703929598</v>
       </c>
       <c r="D27" t="n">
-        <v>0.955663288620604</v>
+        <v>0.9803172703929598</v>
       </c>
       <c r="E27" t="n">
-        <v>85.46000000000001</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>66.70999999999999</v>
+        <v>68.57000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[7, 9, 5, 8, 1]</t>
+          <t>[8, 5, 3, 7, 2]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9432429520821359</v>
+        <v>0.974752040237199</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9432429520821359</v>
+        <v>0.974752040237199</v>
       </c>
       <c r="E28" t="n">
-        <v>96.39</v>
+        <v>91.78</v>
       </c>
       <c r="F28" t="n">
-        <v>68.44</v>
+        <v>76.34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[1, 6, 6, 9, 3]</t>
+          <t>[6, 1, 8, 7, 0]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9496597678045416</v>
+        <v>0.9778794302837107</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9496597678045416</v>
+        <v>0.9778794302837107</v>
       </c>
       <c r="E29" t="n">
-        <v>91.12</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>66.47</v>
+        <v>75.85000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[3, 5, 2, 3, 3]</t>
+          <t>[1, 6, 8, 3, 9]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9695614010075723</v>
+        <v>0.9771019447696719</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9695614010075723</v>
+        <v>0.9771019447696719</v>
       </c>
       <c r="E30" t="n">
-        <v>87.31999999999999</v>
+        <v>92.37</v>
       </c>
       <c r="F30" t="n">
-        <v>68.90000000000001</v>
+        <v>72.60000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[4, 6, 3, 2, 5]</t>
+          <t>[8, 2, 2, 9, 5]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9648714732704561</v>
+        <v>0.9568808959258244</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9648714732704561</v>
+        <v>0.9568808959258244</v>
       </c>
       <c r="E31" t="n">
-        <v>94.38</v>
+        <v>93.87</v>
       </c>
       <c r="F31" t="n">
-        <v>78</v>
+        <v>66.24000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[3, 9, 0, 6, 7]</t>
+          <t>[8, 9, 1, 9, 4]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.967383584372226</v>
+        <v>0.9487511332368089</v>
       </c>
       <c r="D32" t="n">
-        <v>0.967383584372226</v>
+        <v>0.9487511332368089</v>
       </c>
       <c r="E32" t="n">
-        <v>95.23</v>
+        <v>92.77000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>78.32000000000001</v>
+        <v>64.89999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[3, 9, 4, 9, 5]</t>
+          <t>[0, 5, 9, 6, 7]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9485424429234302</v>
+        <v>0.9754454480696765</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9485424429234302</v>
+        <v>0.9754454480696765</v>
       </c>
       <c r="E33" t="n">
-        <v>78.8</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>65.95</v>
+        <v>79.83</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[8, 7, 7, 9, 4]</t>
+          <t>[7, 9, 1, 3, 0]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1240,94 +1240,94 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9382105752039229</v>
+        <v>0.9586342950568515</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9382105752039229</v>
+        <v>0.9586342950568515</v>
       </c>
       <c r="E34" t="n">
-        <v>88.24000000000001</v>
+        <v>77.63</v>
       </c>
       <c r="F34" t="n">
-        <v>70.83</v>
+        <v>67.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[3, 8, 4, 5, 3]</t>
+          <t>[0, 0, 0, 8, 5]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9778527649486021</v>
+        <v>0.9788389286253897</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9778527649486021</v>
+        <v>0.9788389286253897</v>
       </c>
       <c r="E35" t="n">
-        <v>90.16</v>
+        <v>79.24000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>70.44</v>
+        <v>75.56999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[1, 3, 5, 7, 0]</t>
+          <t>[5, 8, 7, 1, 4]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9620170166859339</v>
+        <v>0.9739093282637715</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9620170166859339</v>
+        <v>0.9739093282637715</v>
       </c>
       <c r="E36" t="n">
-        <v>85.99000000000001</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>66.75</v>
+        <v>74.84</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[5, 3, 6, 6, 6]</t>
+          <t>[7, 8, 8, 9, 1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9720291710644789</v>
+        <v>0.9667533860393791</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9720291710644789</v>
+        <v>0.9667533860393791</v>
       </c>
       <c r="E37" t="n">
-        <v>96.12</v>
+        <v>92.09</v>
       </c>
       <c r="F37" t="n">
-        <v>69.88</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[2, 6, 1, 3, 2]</t>
+          <t>[1, 9, 2, 2, 3]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1336,22 +1336,22 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9649783310809342</v>
+        <v>0.9630377281083545</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9649783310809342</v>
+        <v>0.9630377281083545</v>
       </c>
       <c r="E38" t="n">
-        <v>91.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>74.65000000000001</v>
+        <v>68.62</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[9, 7, 8, 9, 9]</t>
+          <t>[2, 4, 9, 3, 4]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1360,22 +1360,22 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9344195387987428</v>
+        <v>0.9605869418014963</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9344195387987428</v>
+        <v>0.9605869418014963</v>
       </c>
       <c r="E39" t="n">
-        <v>92.93000000000001</v>
+        <v>99.96000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>71.96000000000001</v>
+        <v>75.03</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[9, 3, 3, 6, 5]</t>
+          <t>[5, 6, 4, 5, 8]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1384,46 +1384,46 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9748183304877425</v>
+        <v>0.9737854504754582</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9748183304877425</v>
+        <v>0.9737854504754582</v>
       </c>
       <c r="E40" t="n">
-        <v>92.03999999999999</v>
+        <v>96.38000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>68.8</v>
+        <v>77.98</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[0, 7, 6, 9, 9]</t>
+          <t>[5, 2, 3, 5, 1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9490832742370341</v>
+        <v>0.9786368850354843</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9490832742370341</v>
+        <v>0.9786368850354843</v>
       </c>
       <c r="E41" t="n">
-        <v>87.13</v>
+        <v>95.13</v>
       </c>
       <c r="F41" t="n">
-        <v>73.29000000000001</v>
+        <v>73.08</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[0, 8, 3, 0, 4]</t>
+          <t>[6, 5, 7, 0, 4]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1432,22 +1432,22 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9669064281415869</v>
+        <v>0.9590771248127227</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9669064281415869</v>
+        <v>0.9590771248127227</v>
       </c>
       <c r="E42" t="n">
-        <v>71.14</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>72.31</v>
+        <v>70.62</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[4, 7, 9, 0, 8]</t>
+          <t>[7, 8, 4, 3, 2]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1456,70 +1456,70 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9537152189022599</v>
+        <v>0.9586225440772583</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9537152189022599</v>
+        <v>0.9586225440772583</v>
       </c>
       <c r="E43" t="n">
-        <v>82.25</v>
+        <v>85.23</v>
       </c>
       <c r="F43" t="n">
-        <v>74.05</v>
+        <v>69.89000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[9, 5, 7, 3, 5]</t>
+          <t>[5, 0, 4, 5, 5]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9660013085719255</v>
+        <v>0.9655180875755828</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9660013085719255</v>
+        <v>0.9655180875755828</v>
       </c>
       <c r="E44" t="n">
-        <v>99.53</v>
+        <v>88.58000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>71.13</v>
+        <v>75.83</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[0, 3, 3, 0, 5]</t>
+          <t>[3, 1, 1, 0, 9]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9752016263835088</v>
+        <v>0.9695821949922765</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9752016263835088</v>
+        <v>0.9695821949922765</v>
       </c>
       <c r="E45" t="n">
-        <v>85.52</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>75.31999999999999</v>
+        <v>61.81</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[3, 1, 9, 0, 6]</t>
+          <t>[7, 2, 5, 1, 8]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1528,70 +1528,70 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9633889275079145</v>
+        <v>0.9612926261940751</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9633889275079145</v>
+        <v>0.9612926261940751</v>
       </c>
       <c r="E46" t="n">
-        <v>86.62</v>
+        <v>79.72</v>
       </c>
       <c r="F46" t="n">
-        <v>70.26000000000001</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[7, 5, 5, 5, 4]</t>
+          <t>[8, 9, 3, 5, 7]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.9537520314562707</v>
+        <v>0.9552920041851293</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9537520314562707</v>
+        <v>0.9552920041851293</v>
       </c>
       <c r="E47" t="n">
-        <v>80.65000000000001</v>
+        <v>88.83</v>
       </c>
       <c r="F47" t="n">
-        <v>61.38</v>
+        <v>79.58000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[5, 3, 7, 8, 5]</t>
+          <t>[4, 7, 5, 5, 8]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9565544296694727</v>
+        <v>0.9732499159753669</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9565544296694727</v>
+        <v>0.9732499159753669</v>
       </c>
       <c r="E48" t="n">
-        <v>99.78999999999999</v>
+        <v>88.83</v>
       </c>
       <c r="F48" t="n">
-        <v>69.70999999999999</v>
+        <v>76.16</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[5, 2, 3, 2, 6]</t>
+          <t>[7, 8, 7, 2, 2]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1600,22 +1600,22 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.966504712008936</v>
+        <v>0.956091928469214</v>
       </c>
       <c r="D49" t="n">
-        <v>0.966504712008936</v>
+        <v>0.956091928469214</v>
       </c>
       <c r="E49" t="n">
-        <v>83.69999999999999</v>
+        <v>85.03</v>
       </c>
       <c r="F49" t="n">
-        <v>70.01000000000001</v>
+        <v>72.86</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[5, 7, 2, 7, 4]</t>
+          <t>[1, 3, 1, 1, 0]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1624,40 +1624,40 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.953038153871152</v>
+        <v>0.9705776418918768</v>
       </c>
       <c r="D50" t="n">
-        <v>0.953038153871152</v>
+        <v>0.9705776418918768</v>
       </c>
       <c r="E50" t="n">
-        <v>85.74000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>71.28999999999999</v>
+        <v>58.39</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[4, 7, 1, 9, 1]</t>
+          <t>[6, 1, 8, 8, 3]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.9521242789993772</v>
+        <v>0.9810291207038105</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9521242789993772</v>
+        <v>0.9810291207038105</v>
       </c>
       <c r="E51" t="n">
-        <v>98.17</v>
+        <v>99.78</v>
       </c>
       <c r="F51" t="n">
-        <v>74.74000000000001</v>
+        <v>77.08999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_3.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_3.xlsx
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[8, 8, 3, 8, 3]</t>
+          <t>[9, 5, 3, 4, 1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -472,142 +472,142 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9523548174993759</v>
+        <v>0.9541072510161346</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9523548174993759</v>
+        <v>0.9541072510161346</v>
       </c>
       <c r="E2" t="n">
-        <v>71.78999999999999</v>
+        <v>86.33999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>52.78000000000001</v>
+        <v>62.75999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[9, 6, 1, 6, 8]</t>
+          <t>[0, 1, 8, 6, 4]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9748122188995546</v>
+        <v>0.9595733607386309</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9748122188995546</v>
+        <v>0.9595733607386309</v>
       </c>
       <c r="E3" t="n">
-        <v>90.72</v>
+        <v>96.19999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>73.18000000000001</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[2, 5, 5, 3, 1]</t>
+          <t>[2, 3, 9, 5, 8]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9784457206442835</v>
+        <v>0.9560929156673065</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9784457206442835</v>
+        <v>0.9560929156673065</v>
       </c>
       <c r="E4" t="n">
-        <v>96.24000000000001</v>
+        <v>77.69</v>
       </c>
       <c r="F4" t="n">
-        <v>74.03</v>
+        <v>65.53999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[6, 8, 5, 3, 5]</t>
+          <t>[6, 5, 9, 3, 8]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[1, 2, 2, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.991346541033757</v>
+        <v>0.9729186619197012</v>
       </c>
       <c r="D5" t="n">
-        <v>0.991346541033757</v>
+        <v>0.9729186619197012</v>
       </c>
       <c r="E5" t="n">
-        <v>97.22</v>
+        <v>91.50999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>78.31</v>
+        <v>77.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[0, 5, 6, 7, 1]</t>
+          <t>[7, 0, 1, 3, 1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9623043882032117</v>
+        <v>0.977983484614403</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9623043882032117</v>
+        <v>0.977983484614403</v>
       </c>
       <c r="E6" t="n">
-        <v>85.47</v>
+        <v>98.88</v>
       </c>
       <c r="F6" t="n">
-        <v>75.75</v>
+        <v>68.53999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[5, 7, 8, 5, 8]</t>
+          <t>[0, 4, 6, 2, 7]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9751773529514862</v>
+        <v>0.9627401593037235</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9751773529514862</v>
+        <v>0.9627401593037235</v>
       </c>
       <c r="E7" t="n">
-        <v>96.40000000000002</v>
+        <v>93.50999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>76.34</v>
+        <v>70.95999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[2, 9, 5, 5, 0]</t>
+          <t>[1, 8, 2, 3, 6]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -616,22 +616,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9767725249917432</v>
+        <v>0.9817778044897021</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9767725249917432</v>
+        <v>0.9817778044897021</v>
       </c>
       <c r="E8" t="n">
-        <v>97.40000000000001</v>
+        <v>95.53000000000002</v>
       </c>
       <c r="F8" t="n">
-        <v>77.82000000000001</v>
+        <v>74.37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[5, 6, 6, 0, 1]</t>
+          <t>[3, 3, 3, 6, 3]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,142 +640,142 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9749148737824358</v>
+        <v>0.980631790325265</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9749148737824358</v>
+        <v>0.980631790325265</v>
       </c>
       <c r="E9" t="n">
-        <v>82.56</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>74.78</v>
+        <v>60.98</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[4, 7, 5, 0, 5]</t>
+          <t>[8, 9, 8, 3, 0]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9616764806447367</v>
+        <v>0.9629780904817867</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9616764806447367</v>
+        <v>0.9629780904817867</v>
       </c>
       <c r="E10" t="n">
-        <v>73.94</v>
+        <v>96.19</v>
       </c>
       <c r="F10" t="n">
-        <v>69.09</v>
+        <v>75.92999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[6, 3, 3, 1, 6]</t>
+          <t>[3, 3, 4, 5, 9]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9811741550728131</v>
+        <v>0.9616892132714078</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9811741550728131</v>
+        <v>0.9616892132714078</v>
       </c>
       <c r="E11" t="n">
-        <v>87.27</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>73.83000000000001</v>
+        <v>60.77999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[3, 3, 8, 2, 6]</t>
+          <t>[3, 8, 3, 1, 3]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9652236619239314</v>
+        <v>0.9772496532542592</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9652236619239314</v>
+        <v>0.9772496532542592</v>
       </c>
       <c r="E12" t="n">
-        <v>92.74000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>75.66</v>
+        <v>65.21000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[1, 0, 1, 7, 5]</t>
+          <t>[0, 9, 3, 8, 2]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9673570125253914</v>
+        <v>0.9628319876372531</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9673570125253914</v>
+        <v>0.9628319876372531</v>
       </c>
       <c r="E13" t="n">
-        <v>72.3</v>
+        <v>97.42000000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>62.79</v>
+        <v>71.39999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[8, 9, 6, 0, 0]</t>
+          <t>[5, 3, 1, 3, 6]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9746387001203755</v>
+        <v>0.9656902483408367</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9746387001203755</v>
+        <v>0.9656902483408367</v>
       </c>
       <c r="E14" t="n">
-        <v>87.70000000000002</v>
+        <v>77</v>
       </c>
       <c r="F14" t="n">
-        <v>73.23</v>
+        <v>57.87</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[9, 9, 8, 5, 6]</t>
+          <t>[8, 3, 8, 0, 3]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -784,46 +784,46 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.943512371817541</v>
+        <v>0.9538185197640001</v>
       </c>
       <c r="D15" t="n">
-        <v>0.943512371817541</v>
+        <v>0.9538185197640001</v>
       </c>
       <c r="E15" t="n">
-        <v>82.31000000000002</v>
+        <v>76.67</v>
       </c>
       <c r="F15" t="n">
-        <v>62.11</v>
+        <v>61.21999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[5, 3, 5, 8, 5]</t>
+          <t>[3, 6, 5, 3, 9]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9770775842779535</v>
+        <v>0.9760487570294676</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9770775842779535</v>
+        <v>0.9760487570294676</v>
       </c>
       <c r="E16" t="n">
-        <v>97.42</v>
+        <v>86.17</v>
       </c>
       <c r="F16" t="n">
-        <v>78.87</v>
+        <v>67.96000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[3, 9, 2, 0, 3]</t>
+          <t>[6, 9, 9, 5, 1]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -832,46 +832,46 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9628934893227344</v>
+        <v>0.935918848548509</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9628934893227344</v>
+        <v>0.935918848548509</v>
       </c>
       <c r="E17" t="n">
-        <v>85.91</v>
+        <v>83.88</v>
       </c>
       <c r="F17" t="n">
-        <v>68.28999999999999</v>
+        <v>63.14999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[7, 5, 4, 6, 8]</t>
+          <t>[3, 6, 1, 9, 5]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9750886966351833</v>
+        <v>0.9629991257886313</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9750886966351833</v>
+        <v>0.9629991257886313</v>
       </c>
       <c r="E18" t="n">
-        <v>88.29000000000001</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>77.69</v>
+        <v>71.92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[5, 6, 5, 5, 0]</t>
+          <t>[6, 9, 8, 9, 6]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -880,286 +880,286 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9740383454531771</v>
+        <v>0.9585780835080077</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9740383454531771</v>
+        <v>0.9585780835080077</v>
       </c>
       <c r="E19" t="n">
-        <v>80.34</v>
+        <v>96.67999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>73.91</v>
+        <v>79.95</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[5, 8, 5, 5, 6]</t>
+          <t>[3, 7, 5, 3, 7]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 2, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9930050318088361</v>
+        <v>0.9763794583161961</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9930050318088361</v>
+        <v>0.9763794583161961</v>
       </c>
       <c r="E20" t="n">
-        <v>95.77000000000001</v>
+        <v>77.52</v>
       </c>
       <c r="F20" t="n">
-        <v>79.44999999999999</v>
+        <v>75.38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[8, 6, 2, 3, 9]</t>
+          <t>[5, 3, 1, 8, 3]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9755744197481937</v>
+        <v>0.9629100515755615</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9755744197481937</v>
+        <v>0.9629100515755615</v>
       </c>
       <c r="E21" t="n">
-        <v>98.61</v>
+        <v>87.22999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>77.47000000000001</v>
+        <v>69.55</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[6, 5, 2, 5, 1]</t>
+          <t>[4, 5, 6, 6, 2]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9619311515094581</v>
+        <v>0.950094781775198</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9619311515094581</v>
+        <v>0.950094781775198</v>
       </c>
       <c r="E22" t="n">
-        <v>96.24000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>73</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[3, 0, 5, 8, 0]</t>
+          <t>[4, 4, 2, 7, 1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9786324543950282</v>
+        <v>0.9585419074494443</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9786324543950282</v>
+        <v>0.9585419074494443</v>
       </c>
       <c r="E23" t="n">
-        <v>83.14</v>
+        <v>96.64999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>72.93000000000001</v>
+        <v>74.41999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[1, 0, 6, 6, 6]</t>
+          <t>[6, 6, 5, 3, 1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9790507664171814</v>
+        <v>0.9526452642710385</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9790507664171814</v>
+        <v>0.9526452642710385</v>
       </c>
       <c r="E24" t="n">
-        <v>82.02</v>
+        <v>81.31</v>
       </c>
       <c r="F24" t="n">
-        <v>76.31</v>
+        <v>62.27</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[6, 6, 6, 9, 8]</t>
+          <t>[8, 3, 5, 0, 6]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9713479034623994</v>
+        <v>0.9707997432105419</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9713479034623994</v>
+        <v>0.9707997432105419</v>
       </c>
       <c r="E25" t="n">
-        <v>94.94</v>
+        <v>94.3</v>
       </c>
       <c r="F25" t="n">
-        <v>76.60000000000001</v>
+        <v>72.73999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[4, 5, 6, 5, 3]</t>
+          <t>[4, 7, 3, 0, 9]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9765463076207255</v>
+        <v>0.9606634570745334</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9765463076207255</v>
+        <v>0.9606634570745334</v>
       </c>
       <c r="E26" t="n">
-        <v>89.99000000000001</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>76.03999999999999</v>
+        <v>64.44</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[3, 8, 0, 5, 3]</t>
+          <t>[3, 7, 8, 6, 2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9803172703929598</v>
+        <v>0.9656489264039467</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9803172703929598</v>
+        <v>0.9656489264039467</v>
       </c>
       <c r="E27" t="n">
-        <v>84.31999999999999</v>
+        <v>88.16999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>68.57000000000001</v>
+        <v>79.61999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[8, 5, 3, 7, 2]</t>
+          <t>[9, 2, 7, 4, 3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.974752040237199</v>
+        <v>0.9478367943489209</v>
       </c>
       <c r="D28" t="n">
-        <v>0.974752040237199</v>
+        <v>0.9478367943489209</v>
       </c>
       <c r="E28" t="n">
-        <v>91.78</v>
+        <v>82.97</v>
       </c>
       <c r="F28" t="n">
-        <v>76.34</v>
+        <v>68.43000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[6, 1, 8, 7, 0]</t>
+          <t>[5, 5, 6, 7, 1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9778794302837107</v>
+        <v>0.9482429521187609</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9778794302837107</v>
+        <v>0.9482429521187609</v>
       </c>
       <c r="E29" t="n">
-        <v>82.51000000000001</v>
+        <v>79.13</v>
       </c>
       <c r="F29" t="n">
-        <v>75.85000000000001</v>
+        <v>69.44</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[1, 6, 8, 3, 9]</t>
+          <t>[3, 7, 9, 1, 7]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9771019447696719</v>
+        <v>0.9692513240577375</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9771019447696719</v>
+        <v>0.9692513240577375</v>
       </c>
       <c r="E30" t="n">
-        <v>92.37</v>
+        <v>92.19999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>72.60000000000001</v>
+        <v>77.64</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[8, 2, 2, 9, 5]</t>
+          <t>[5, 7, 9, 8, 9]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1168,70 +1168,70 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9568808959258244</v>
+        <v>0.9353674520217472</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9568808959258244</v>
+        <v>0.9353674520217472</v>
       </c>
       <c r="E31" t="n">
-        <v>93.87</v>
+        <v>74.10999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>66.24000000000001</v>
+        <v>70.65000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[8, 9, 1, 9, 4]</t>
+          <t>[6, 6, 8, 3, 4]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9487511332368089</v>
+        <v>0.9648920511119572</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9487511332368089</v>
+        <v>0.9648920511119572</v>
       </c>
       <c r="E32" t="n">
-        <v>92.77000000000001</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>64.89999999999999</v>
+        <v>78.67999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[0, 5, 9, 6, 7]</t>
+          <t>[3, 5, 4, 9, 9]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9754454480696765</v>
+        <v>0.9503623801011306</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9754454480696765</v>
+        <v>0.9503623801011306</v>
       </c>
       <c r="E33" t="n">
-        <v>86.93000000000001</v>
+        <v>82.86999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>79.83</v>
+        <v>63.42</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[7, 9, 1, 3, 0]</t>
+          <t>[1, 1, 8, 2, 1]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1240,70 +1240,70 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9586342950568515</v>
+        <v>0.9654565648501684</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9586342950568515</v>
+        <v>0.9654565648501684</v>
       </c>
       <c r="E34" t="n">
-        <v>77.63</v>
+        <v>92.39999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>67.16</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[0, 0, 0, 8, 5]</t>
+          <t>[0, 8, 6, 1, 5]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9788389286253897</v>
+        <v>0.9587804809914392</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9788389286253897</v>
+        <v>0.9587804809914392</v>
       </c>
       <c r="E35" t="n">
-        <v>79.24000000000001</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>75.56999999999999</v>
+        <v>65.28999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[5, 8, 7, 1, 4]</t>
+          <t>[6, 9, 7, 7, 0]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9739093282637715</v>
+        <v>0.9342080430020704</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9739093282637715</v>
+        <v>0.9342080430020704</v>
       </c>
       <c r="E36" t="n">
-        <v>94.34999999999999</v>
+        <v>79.72</v>
       </c>
       <c r="F36" t="n">
-        <v>74.84</v>
+        <v>69.42</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[7, 8, 8, 9, 1]</t>
+          <t>[0, 5, 7, 3, 9]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1312,46 +1312,46 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9667533860393791</v>
+        <v>0.976972276632885</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9667533860393791</v>
+        <v>0.976972276632885</v>
       </c>
       <c r="E37" t="n">
-        <v>92.09</v>
+        <v>90.63</v>
       </c>
       <c r="F37" t="n">
-        <v>69.09999999999999</v>
+        <v>78.78999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[1, 9, 2, 2, 3]</t>
+          <t>[7, 2, 3, 3, 3]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 2, 1]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9630377281083545</v>
+        <v>0.9953949341980235</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9630377281083545</v>
+        <v>0.9953949341980235</v>
       </c>
       <c r="E38" t="n">
-        <v>97.40000000000001</v>
+        <v>94.60000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>68.62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[2, 4, 9, 3, 4]</t>
+          <t>[4, 2, 8, 7, 4]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1360,70 +1360,70 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9605869418014963</v>
+        <v>0.9532124864501567</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9605869418014963</v>
+        <v>0.9532124864501567</v>
       </c>
       <c r="E39" t="n">
-        <v>99.96000000000001</v>
+        <v>91.64000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>75.03</v>
+        <v>79.08999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[5, 6, 4, 5, 8]</t>
+          <t>[5, 2, 5, 5, 3]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9737854504754582</v>
+        <v>0.9755073358302733</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9737854504754582</v>
+        <v>0.9755073358302733</v>
       </c>
       <c r="E40" t="n">
-        <v>96.38000000000001</v>
+        <v>92.73</v>
       </c>
       <c r="F40" t="n">
-        <v>77.98</v>
+        <v>78.70000000000002</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[5, 2, 3, 5, 1]</t>
+          <t>[3, 3, 0, 0, 3]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9786368850354843</v>
+        <v>0.972272310540871</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9786368850354843</v>
+        <v>0.972272310540871</v>
       </c>
       <c r="E41" t="n">
-        <v>95.13</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>73.08</v>
+        <v>48.69</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[6, 5, 7, 0, 4]</t>
+          <t>[4, 1, 4, 3, 3]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1432,70 +1432,70 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9590771248127227</v>
+        <v>0.9654988803899912</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9590771248127227</v>
+        <v>0.9654988803899912</v>
       </c>
       <c r="E42" t="n">
-        <v>73.40000000000001</v>
+        <v>90.53</v>
       </c>
       <c r="F42" t="n">
-        <v>70.62</v>
+        <v>62.42999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[7, 8, 4, 3, 2]</t>
+          <t>[3, 6, 8, 1, 5]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9586225440772583</v>
+        <v>0.9737410893852197</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9586225440772583</v>
+        <v>0.9737410893852197</v>
       </c>
       <c r="E43" t="n">
-        <v>85.23</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>69.89000000000001</v>
+        <v>78.34999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[5, 0, 4, 5, 5]</t>
+          <t>[0, 7, 6, 3, 3]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9655180875755828</v>
+        <v>0.9770983126537465</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9655180875755828</v>
+        <v>0.9770983126537465</v>
       </c>
       <c r="E44" t="n">
-        <v>88.58000000000001</v>
+        <v>88.92</v>
       </c>
       <c r="F44" t="n">
-        <v>75.83</v>
+        <v>76.21000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[3, 1, 1, 0, 9]</t>
+          <t>[4, 8, 0, 0, 3]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1504,22 +1504,22 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9695821949922765</v>
+        <v>0.9647140775088795</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9695821949922765</v>
+        <v>0.9647140775088795</v>
       </c>
       <c r="E45" t="n">
-        <v>81.31999999999999</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>61.81</v>
+        <v>61.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[7, 2, 5, 1, 8]</t>
+          <t>[9, 0, 3, 6, 8]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1528,22 +1528,22 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9612926261940751</v>
+        <v>0.9533155730758898</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9612926261940751</v>
+        <v>0.9533155730758898</v>
       </c>
       <c r="E46" t="n">
-        <v>79.72</v>
+        <v>82.52000000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>63.3</v>
+        <v>61.61</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[8, 9, 3, 5, 7]</t>
+          <t>[3, 7, 5, 6, 1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1552,46 +1552,46 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.9552920041851293</v>
+        <v>0.953927386151847</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9552920041851293</v>
+        <v>0.953927386151847</v>
       </c>
       <c r="E47" t="n">
-        <v>88.83</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>79.58000000000001</v>
+        <v>76.50999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[4, 7, 5, 5, 8]</t>
+          <t>[3, 3, 1, 9, 3]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9732499159753669</v>
+        <v>0.9801791438707349</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9732499159753669</v>
+        <v>0.9801791438707349</v>
       </c>
       <c r="E48" t="n">
-        <v>88.83</v>
+        <v>89.63</v>
       </c>
       <c r="F48" t="n">
-        <v>76.16</v>
+        <v>63.84</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[7, 8, 7, 2, 2]</t>
+          <t>[3, 2, 1, 1, 6]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1600,22 +1600,22 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.956091928469214</v>
+        <v>0.9706114004187155</v>
       </c>
       <c r="D49" t="n">
-        <v>0.956091928469214</v>
+        <v>0.9706114004187155</v>
       </c>
       <c r="E49" t="n">
-        <v>85.03</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>72.86</v>
+        <v>60.27</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[1, 3, 1, 1, 0]</t>
+          <t>[0, 8, 5, 2, 0]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1624,40 +1624,40 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.9705776418918768</v>
+        <v>0.9626592648683023</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9705776418918768</v>
+        <v>0.9626592648683023</v>
       </c>
       <c r="E50" t="n">
-        <v>77.09999999999999</v>
+        <v>93.59</v>
       </c>
       <c r="F50" t="n">
-        <v>58.39</v>
+        <v>64.44</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[6, 1, 8, 8, 3]</t>
+          <t>[3, 2, 5, 9, 4]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[2, 1, 2, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.9810291207038105</v>
+        <v>0.9740090975934748</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9810291207038105</v>
+        <v>0.9740090975934748</v>
       </c>
       <c r="E51" t="n">
-        <v>99.78</v>
+        <v>98.63999999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>77.08999999999999</v>
+        <v>74.97</v>
       </c>
     </row>
   </sheetData>

--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_3.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_3.xlsx
@@ -463,79 +463,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[9, 1, 3, 5, 0]</t>
+          <t>[2, 3, 5, 3, 0]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 2, 1]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9494129704927208</v>
+        <v>0.9928111783597182</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9494129704927208</v>
+        <v>0.9928111783597182</v>
       </c>
       <c r="E2" t="n">
-        <v>97.22</v>
+        <v>114.4</v>
       </c>
       <c r="F2" t="n">
-        <v>73.59</v>
+        <v>96.65000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[2, 5, 7, 8, 9]</t>
+          <t>[1, 4, 2, 3, 1]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 3, 1]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9336799012644394</v>
+        <v>0.9794304845433669</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9336799012644394</v>
+        <v>0.9794304845433669</v>
       </c>
       <c r="E3" t="n">
-        <v>96.69</v>
+        <v>115</v>
       </c>
       <c r="F3" t="n">
-        <v>67.90000000000001</v>
+        <v>95.46000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[4, 7, 3, 6, 4]</t>
+          <t>[7, 4, 3, 0, 0]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9402228162520373</v>
+        <v>0.9577275659057268</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9402228162520373</v>
+        <v>0.9577275659057268</v>
       </c>
       <c r="E4" t="n">
-        <v>79.87</v>
+        <v>113.99</v>
       </c>
       <c r="F4" t="n">
-        <v>70.78</v>
+        <v>84.61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[2, 4, 7, 3, 0]</t>
+          <t>[6, 5, 5, 1, 1]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -544,334 +544,334 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9504256012523508</v>
+        <v>0.9508837471372029</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9504256012523508</v>
+        <v>0.9508837471372029</v>
       </c>
       <c r="E5" t="n">
-        <v>86.49000000000001</v>
+        <v>71.66</v>
       </c>
       <c r="F5" t="n">
-        <v>74.58000000000001</v>
+        <v>73.51000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[7, 3, 0, 3, 5]</t>
+          <t>[1, 0, 5, 0, 5]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9537541694989112</v>
+        <v>0.9748673054375053</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9537541694989112</v>
+        <v>0.9748673054375053</v>
       </c>
       <c r="E6" t="n">
-        <v>97.5</v>
+        <v>108.32</v>
       </c>
       <c r="F6" t="n">
-        <v>76.02</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[1, 1, 4, 6, 2]</t>
+          <t>[6, 9, 5, 1, 4]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9756415213435847</v>
+        <v>0.9684817608689189</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9756415213435847</v>
+        <v>0.9684817608689189</v>
       </c>
       <c r="E7" t="n">
-        <v>89.5</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>77.88</v>
+        <v>85.66</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 6, 1]</t>
+          <t>[6, 6, 7, 7, 1]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[2, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9781066243718172</v>
+        <v>0.9692963823009932</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9781066243718172</v>
+        <v>0.9692963823009932</v>
       </c>
       <c r="E8" t="n">
-        <v>97.71000000000001</v>
+        <v>105.08</v>
       </c>
       <c r="F8" t="n">
-        <v>75.60000000000001</v>
+        <v>94.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[5, 8, 4, 6, 1]</t>
+          <t>[4, 3, 5, 2, 1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9361957383909005</v>
+        <v>0.973732808776727</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9361957383909005</v>
+        <v>0.973732808776727</v>
       </c>
       <c r="E9" t="n">
-        <v>88.01000000000001</v>
+        <v>93.02000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>65.22</v>
+        <v>85.97999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[9, 9, 3, 1, 2]</t>
+          <t>[6, 7, 4, 7, 3]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 2, 2, 1]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9470532685327961</v>
+        <v>0.995178719095167</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9470532685327961</v>
+        <v>0.995178719095167</v>
       </c>
       <c r="E10" t="n">
-        <v>85.59</v>
+        <v>116.67</v>
       </c>
       <c r="F10" t="n">
-        <v>72.72</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[1, 8, 2, 9, 6]</t>
+          <t>[1, 5, 7, 4, 7]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9429918614363466</v>
+        <v>0.9702662929835966</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9429918614363466</v>
+        <v>0.9702662929835966</v>
       </c>
       <c r="E11" t="n">
-        <v>86.96000000000001</v>
+        <v>82.13</v>
       </c>
       <c r="F11" t="n">
-        <v>64.72999999999999</v>
+        <v>77.49999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[5, 1, 9, 6, 4]</t>
+          <t>[8, 2, 7, 3, 6]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 3]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9412716920103611</v>
+        <v>0.9511760179783419</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9412716920103611</v>
+        <v>0.9511760179783419</v>
       </c>
       <c r="E12" t="n">
-        <v>89.81</v>
+        <v>118.81</v>
       </c>
       <c r="F12" t="n">
-        <v>67.55</v>
+        <v>94.78</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[4, 3, 1, 3, 3]</t>
+          <t>[1, 5, 6, 2, 5]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9598300665837061</v>
+        <v>0.9572425564070258</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9598300665837061</v>
+        <v>0.9572425564070258</v>
       </c>
       <c r="E13" t="n">
-        <v>74.02000000000001</v>
+        <v>88.80000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>78.13000000000001</v>
+        <v>89.48999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[4, 3, 0, 2, 8]</t>
+          <t>[5, 1, 0, 0, 1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9602539132801829</v>
+        <v>0.976211296920186</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9602539132801829</v>
+        <v>0.976211296920186</v>
       </c>
       <c r="E14" t="n">
-        <v>84.02000000000001</v>
+        <v>111.31</v>
       </c>
       <c r="F14" t="n">
-        <v>78.09999999999999</v>
+        <v>93.96000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[4, 4, 4, 0, 2]</t>
+          <t>[4, 3, 4, 3, 7]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 3]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9588576503020867</v>
+        <v>0.975488630996128</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9588576503020867</v>
+        <v>0.975488630996128</v>
       </c>
       <c r="E15" t="n">
-        <v>75.86</v>
+        <v>118.95</v>
       </c>
       <c r="F15" t="n">
-        <v>79.47999999999999</v>
+        <v>95.14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[3, 6, 2, 8, 7]</t>
+          <t>[8, 6, 0, 9, 5]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9407762053246869</v>
+        <v>0.9482557296026123</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9407762053246869</v>
+        <v>0.9482557296026123</v>
       </c>
       <c r="E16" t="n">
-        <v>87.23999999999998</v>
+        <v>104.01</v>
       </c>
       <c r="F16" t="n">
-        <v>67.16</v>
+        <v>88.29000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[0, 1, 1, 1, 5]</t>
+          <t>[3, 0, 6, 5, 6]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9728492369819701</v>
+        <v>0.9568966061632782</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9728492369819701</v>
+        <v>0.9568966061632782</v>
       </c>
       <c r="E17" t="n">
-        <v>93.07999999999998</v>
+        <v>100.54</v>
       </c>
       <c r="F17" t="n">
-        <v>59.46</v>
+        <v>82.96000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[6, 8, 8, 4, 7]</t>
+          <t>[0, 1, 4, 8, 3]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9305792180519352</v>
+        <v>0.9718627159260915</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9305792180519352</v>
+        <v>0.9718627159260915</v>
       </c>
       <c r="E18" t="n">
-        <v>88.63</v>
+        <v>109.52</v>
       </c>
       <c r="F18" t="n">
-        <v>62.95</v>
+        <v>83.36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[7, 5, 3, 6, 7]</t>
+          <t>[0, 2, 2, 2, 5]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -880,784 +880,784 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9342602716757482</v>
+        <v>0.958974455943257</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9342602716757482</v>
+        <v>0.958974455943257</v>
       </c>
       <c r="E19" t="n">
-        <v>98.19999999999999</v>
+        <v>95.49999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>63.39</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[0, 0, 8, 6, 3]</t>
+          <t>[4, 3, 7, 7, 1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9562025985314457</v>
+        <v>0.9747813814101193</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9562025985314457</v>
+        <v>0.9747813814101193</v>
       </c>
       <c r="E20" t="n">
-        <v>98.56000000000002</v>
+        <v>102.95</v>
       </c>
       <c r="F20" t="n">
-        <v>75.06</v>
+        <v>87.57999999999998</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[9, 3, 1, 1, 1]</t>
+          <t>[0, 5, 5, 8, 7]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9630813009549035</v>
+        <v>0.9722980247600485</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9630813009549035</v>
+        <v>0.9722980247600485</v>
       </c>
       <c r="E21" t="n">
-        <v>97.85999999999999</v>
+        <v>92.89999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>70.17000000000002</v>
+        <v>85.23999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[3, 0, 2, 1, 1]</t>
+          <t>[3, 1, 2, 3, 6]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 2, 1]</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9667947897526333</v>
+        <v>0.993802357375809</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9667947897526333</v>
+        <v>0.993802357375809</v>
       </c>
       <c r="E22" t="n">
-        <v>84.2</v>
+        <v>119.01</v>
       </c>
       <c r="F22" t="n">
-        <v>67.99000000000001</v>
+        <v>97.46000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 3, 1]</t>
+          <t>[7, 9, 3, 6, 8]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9782043149430041</v>
+        <v>0.9672577106770969</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9782043149430041</v>
+        <v>0.9672577106770969</v>
       </c>
       <c r="E23" t="n">
-        <v>92.15000000000001</v>
+        <v>101.24</v>
       </c>
       <c r="F23" t="n">
-        <v>70.36000000000001</v>
+        <v>79.69999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[4, 1, 3, 1, 0]</t>
+          <t>[7, 8, 5, 1, 1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9760695739271019</v>
+        <v>0.951280432304638</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9760695739271019</v>
+        <v>0.951280432304638</v>
       </c>
       <c r="E24" t="n">
-        <v>98.09</v>
+        <v>91.3</v>
       </c>
       <c r="F24" t="n">
-        <v>77.88</v>
+        <v>86.44</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[8, 2, 3, 4, 6]</t>
+          <t>[4, 1, 4, 2, 7]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9475510081811864</v>
+        <v>0.9731357200544124</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9475510081811864</v>
+        <v>0.9731357200544124</v>
       </c>
       <c r="E25" t="n">
-        <v>79.13</v>
+        <v>102.82</v>
       </c>
       <c r="F25" t="n">
-        <v>73.75</v>
+        <v>86.97</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[0, 7, 6, 7, 3]</t>
+          <t>[4, 1, 4, 3, 2]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9396032504180181</v>
+        <v>0.9938627101148372</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9396032504180181</v>
+        <v>0.9938627101148372</v>
       </c>
       <c r="E26" t="n">
-        <v>98.56</v>
+        <v>118.66</v>
       </c>
       <c r="F26" t="n">
-        <v>64.57000000000001</v>
+        <v>98.58</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[1, 1, 7, 1, 1]</t>
+          <t>[2, 3, 4, 1, 4]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 2]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9645480470317366</v>
+        <v>0.9768135796034875</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9645480470317366</v>
+        <v>0.9768135796034875</v>
       </c>
       <c r="E27" t="n">
-        <v>83.30000000000001</v>
+        <v>118.66</v>
       </c>
       <c r="F27" t="n">
-        <v>46.7</v>
+        <v>98.58</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[3, 1, 6, 2, 1]</t>
+          <t>[9, 7, 8, 4, 7]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9711507754756519</v>
+        <v>0.9428786727386017</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9711507754756519</v>
+        <v>0.9428786727386017</v>
       </c>
       <c r="E28" t="n">
-        <v>94.93000000000001</v>
+        <v>94.63000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>72.98</v>
+        <v>77.06</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[3, 1, 1, 5, 2]</t>
+          <t>[5, 4, 7, 7, 0]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 2]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9613672317313543</v>
+        <v>0.9711330581376445</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9613672317313543</v>
+        <v>0.9711330581376445</v>
       </c>
       <c r="E29" t="n">
-        <v>83.84</v>
+        <v>112.55</v>
       </c>
       <c r="F29" t="n">
-        <v>66.81</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[4, 6, 9, 3, 7]</t>
+          <t>[7, 3, 7, 7, 5]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 3]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9392538689507711</v>
+        <v>0.949293257290151</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9392538689507711</v>
+        <v>0.949293257290151</v>
       </c>
       <c r="E30" t="n">
-        <v>87.31</v>
+        <v>89.58000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>70.04000000000001</v>
+        <v>89.48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[9, 2, 5, 3, 5]</t>
+          <t>[4, 3, 4, 6, 9]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9408409319009683</v>
+        <v>0.9712813483430586</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9408409319009683</v>
+        <v>0.9712813483430586</v>
       </c>
       <c r="E31" t="n">
-        <v>95.68000000000001</v>
+        <v>101.94</v>
       </c>
       <c r="F31" t="n">
-        <v>78.45</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[1, 8, 9, 1, 6]</t>
+          <t>[5, 2, 2, 1, 2]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9515953753177392</v>
+        <v>0.9760758909875676</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9515953753177392</v>
+        <v>0.9760758909875676</v>
       </c>
       <c r="E32" t="n">
-        <v>88.13999999999999</v>
+        <v>100.19</v>
       </c>
       <c r="F32" t="n">
-        <v>58.69</v>
+        <v>95.28</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[7, 9, 1, 4, 0]</t>
+          <t>[4, 1, 8, 6, 5]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9473287844979135</v>
+        <v>0.989543772470288</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9473287844979135</v>
+        <v>0.989543772470288</v>
       </c>
       <c r="E33" t="n">
-        <v>92.59</v>
+        <v>116.52</v>
       </c>
       <c r="F33" t="n">
-        <v>66.11</v>
+        <v>97.34999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[3, 7, 2, 6, 8]</t>
+          <t>[7, 2, 4, 4, 6]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9408867803034487</v>
+        <v>0.9780314384585858</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9408867803034487</v>
+        <v>0.9780314384585858</v>
       </c>
       <c r="E34" t="n">
-        <v>87.23999999999998</v>
+        <v>113.87</v>
       </c>
       <c r="F34" t="n">
-        <v>67.16</v>
+        <v>92.72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[1, 4, 7, 3, 6]</t>
+          <t>[6, 8, 5, 6, 2]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9722452904788873</v>
+        <v>0.9669134136785942</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9722452904788873</v>
+        <v>0.9669134136785942</v>
       </c>
       <c r="E35" t="n">
-        <v>98.40000000000001</v>
+        <v>103.07</v>
       </c>
       <c r="F35" t="n">
-        <v>73.53</v>
+        <v>86.28</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[6, 6, 4, 7, 8]</t>
+          <t>[3, 0, 8, 3, 2]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9328213543745058</v>
+        <v>0.9563651097174111</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9328213543745058</v>
+        <v>0.9563651097174111</v>
       </c>
       <c r="E36" t="n">
-        <v>88.68000000000001</v>
+        <v>115.23</v>
       </c>
       <c r="F36" t="n">
-        <v>62.05</v>
+        <v>87.15000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[1, 2, 8, 4, 2]</t>
+          <t>[6, 3, 2, 7, 0]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9751080095771358</v>
+        <v>0.9701172093845616</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9751080095771358</v>
+        <v>0.9701172093845616</v>
       </c>
       <c r="E37" t="n">
-        <v>91.18000000000001</v>
+        <v>107.71</v>
       </c>
       <c r="F37" t="n">
-        <v>78.23</v>
+        <v>86.65000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[0, 6, 5, 4, 4]</t>
+          <t>[3, 5, 9, 1, 2]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9498600117702356</v>
+        <v>0.9722143679015732</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9498600117702356</v>
+        <v>0.9722143679015732</v>
       </c>
       <c r="E38" t="n">
-        <v>90.04000000000002</v>
+        <v>98.08</v>
       </c>
       <c r="F38" t="n">
-        <v>75.25999999999999</v>
+        <v>85.37</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[6, 1, 6, 1, 7]</t>
+          <t>[7, 4, 9, 8, 4]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9512145378540593</v>
+        <v>0.9435213996375686</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9512145378540593</v>
+        <v>0.9435213996375686</v>
       </c>
       <c r="E39" t="n">
-        <v>88.85999999999999</v>
+        <v>104.79</v>
       </c>
       <c r="F39" t="n">
-        <v>51.94000000000001</v>
+        <v>80.22</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[6, 2, 2, 1, 7]</t>
+          <t>[2, 9, 1, 7, 3]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9788043407870566</v>
+        <v>0.963858071689335</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9788043407870566</v>
+        <v>0.963858071689335</v>
       </c>
       <c r="E40" t="n">
-        <v>98.16</v>
+        <v>102.69</v>
       </c>
       <c r="F40" t="n">
-        <v>76.78000000000002</v>
+        <v>87.78999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[6, 1, 0, 4, 6]</t>
+          <t>[3, 3, 7, 1, 8]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 2]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9596369071577739</v>
+        <v>0.9771394723039037</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9596369071577739</v>
+        <v>0.9771394723039037</v>
       </c>
       <c r="E41" t="n">
-        <v>88.41999999999999</v>
+        <v>113.02</v>
       </c>
       <c r="F41" t="n">
-        <v>65.5</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[0, 4, 2, 2, 8]</t>
+          <t>[8, 3, 1, 8, 1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9612939056769532</v>
+        <v>0.9896247166768499</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9612939056769532</v>
+        <v>0.9896247166768499</v>
       </c>
       <c r="E42" t="n">
-        <v>83.22999999999999</v>
+        <v>118.78</v>
       </c>
       <c r="F42" t="n">
-        <v>75.86</v>
+        <v>97.54000000000002</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[7, 7, 3, 8, 3]</t>
+          <t>[6, 5, 2, 1, 0]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9311778262676079</v>
+        <v>0.9722489788757419</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9311778262676079</v>
+        <v>0.9722489788757419</v>
       </c>
       <c r="E43" t="n">
-        <v>90.45</v>
+        <v>99.37</v>
       </c>
       <c r="F43" t="n">
-        <v>66.78</v>
+        <v>91.17000000000002</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[1, 1, 6, 8, 5]</t>
+          <t>[9, 3, 5, 0, 7]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 3]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9546966718097344</v>
+        <v>0.9529471473204096</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9546966718097344</v>
+        <v>0.9529471473204096</v>
       </c>
       <c r="E44" t="n">
-        <v>90.92000000000002</v>
+        <v>107.04</v>
       </c>
       <c r="F44" t="n">
-        <v>58.63</v>
+        <v>92.11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[8, 9, 7, 5, 4]</t>
+          <t>[9, 5, 0, 7, 3]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9235145259008268</v>
+        <v>0.9886672968308032</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9235145259008268</v>
+        <v>0.9886672968308032</v>
       </c>
       <c r="E45" t="n">
-        <v>94.96000000000001</v>
+        <v>117.39</v>
       </c>
       <c r="F45" t="n">
-        <v>68.45</v>
+        <v>99.81</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[4, 5, 3, 8, 3]</t>
+          <t>[1, 9, 3, 0, 0]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9403782668109484</v>
+        <v>0.971446890279399</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9403782668109484</v>
+        <v>0.971446890279399</v>
       </c>
       <c r="E46" t="n">
-        <v>84.45</v>
+        <v>110.99</v>
       </c>
       <c r="F46" t="n">
-        <v>79.16000000000001</v>
+        <v>90.24000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[7, 8, 5, 6, 8]</t>
+          <t>[9, 9, 3, 2, 7]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.9246481873357999</v>
+        <v>0.9665617438695038</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9246481873357999</v>
+        <v>0.9665617438695038</v>
       </c>
       <c r="E47" t="n">
-        <v>98.84999999999999</v>
+        <v>102.09</v>
       </c>
       <c r="F47" t="n">
-        <v>62.15</v>
+        <v>82.34999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[6, 1, 4, 3, 8]</t>
+          <t>[4, 9, 5, 7, 2]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[2, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9677412015358932</v>
+        <v>0.9875896347797093</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9677412015358932</v>
+        <v>0.9875896347797093</v>
       </c>
       <c r="E48" t="n">
-        <v>95.93000000000001</v>
+        <v>111.24</v>
       </c>
       <c r="F48" t="n">
-        <v>77.05</v>
+        <v>96.01000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[9, 4, 8, 6, 6]</t>
+          <t>[8, 9, 0, 1, 3]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.9301053261594695</v>
+        <v>0.9541221010422146</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9301053261594695</v>
+        <v>0.9541221010422146</v>
       </c>
       <c r="E49" t="n">
-        <v>88.00999999999999</v>
+        <v>109.39</v>
       </c>
       <c r="F49" t="n">
-        <v>67.90000000000001</v>
+        <v>84.18000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[6, 7, 8, 2, 2]</t>
+          <t>[6, 1, 7, 9, 2]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.935953774925196</v>
+        <v>0.9720483414109085</v>
       </c>
       <c r="D50" t="n">
-        <v>0.935953774925196</v>
+        <v>0.9720483414109085</v>
       </c>
       <c r="E50" t="n">
-        <v>86.45</v>
+        <v>108.29</v>
       </c>
       <c r="F50" t="n">
-        <v>64.92</v>
+        <v>95.91</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[0, 8, 3, 1, 8]</t>
+          <t>[6, 7, 6, 6, 8]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.9581497615989355</v>
+        <v>0.9664081607203033</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9581497615989355</v>
+        <v>0.9664081607203033</v>
       </c>
       <c r="E51" t="n">
-        <v>90.84</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>68.98999999999999</v>
+        <v>77.81999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_3.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_3.xlsx
@@ -463,79 +463,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[2, 3, 5, 3, 0]</t>
+          <t>[7, 5, 2, 7, 7]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 2, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9928111783597182</v>
+        <v>0.9466816710747756</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9928111783597182</v>
+        <v>0.9466816710747756</v>
       </c>
       <c r="E2" t="n">
-        <v>114.4</v>
+        <v>94.06</v>
       </c>
       <c r="F2" t="n">
-        <v>96.65000000000001</v>
+        <v>79.16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[1, 4, 2, 3, 1]</t>
+          <t>[6, 8, 0, 9, 2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 3, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9794304845433669</v>
+        <v>0.9435566893171964</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9794304845433669</v>
+        <v>0.9435566893171964</v>
       </c>
       <c r="E3" t="n">
-        <v>115</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>95.46000000000001</v>
+        <v>69.11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[7, 4, 3, 0, 0]</t>
+          <t>[7, 4, 5, 7, 9]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9577275659057268</v>
+        <v>0.9672279229299359</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9577275659057268</v>
+        <v>0.9672279229299359</v>
       </c>
       <c r="E4" t="n">
-        <v>113.99</v>
+        <v>114.65</v>
       </c>
       <c r="F4" t="n">
-        <v>84.61</v>
+        <v>92.44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[6, 5, 5, 1, 1]</t>
+          <t>[4, 6, 5, 3, 1]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -544,454 +544,454 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9508837471372029</v>
+        <v>0.9429464984496578</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9508837471372029</v>
+        <v>0.9429464984496578</v>
       </c>
       <c r="E5" t="n">
-        <v>71.66</v>
+        <v>98.75</v>
       </c>
       <c r="F5" t="n">
-        <v>73.51000000000001</v>
+        <v>63.45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[1, 0, 5, 0, 5]</t>
+          <t>[9, 1, 1, 8, 0]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9748673054375053</v>
+        <v>0.9497291596264147</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9748673054375053</v>
+        <v>0.9497291596264147</v>
       </c>
       <c r="E6" t="n">
-        <v>108.32</v>
+        <v>89.46000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>93</v>
+        <v>76.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[6, 9, 5, 1, 4]</t>
+          <t>[1, 3, 1, 7, 7]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9684817608689189</v>
+        <v>0.9566995307959721</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9684817608689189</v>
+        <v>0.9566995307959721</v>
       </c>
       <c r="E7" t="n">
-        <v>97.34999999999999</v>
+        <v>100.8</v>
       </c>
       <c r="F7" t="n">
-        <v>85.66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[6, 6, 7, 7, 1]</t>
+          <t>[5, 5, 6, 5, 2]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 3, 1]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9692963823009932</v>
+        <v>0.9668459960725854</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9692963823009932</v>
+        <v>0.9668459960725854</v>
       </c>
       <c r="E8" t="n">
-        <v>105.08</v>
+        <v>116.4</v>
       </c>
       <c r="F8" t="n">
-        <v>94.67</v>
+        <v>73.41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[4, 3, 5, 2, 1]</t>
+          <t>[0, 2, 1, 1, 6]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.973732808776727</v>
+        <v>0.9646245355528287</v>
       </c>
       <c r="D9" t="n">
-        <v>0.973732808776727</v>
+        <v>0.9646245355528287</v>
       </c>
       <c r="E9" t="n">
-        <v>93.02000000000001</v>
+        <v>99.22</v>
       </c>
       <c r="F9" t="n">
-        <v>85.97999999999999</v>
+        <v>67.47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[6, 7, 4, 7, 3]</t>
+          <t>[1, 5, 4, 7, 8]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[1, 2, 2, 2, 1]</t>
+          <t>[1, 1, 1, 3, 1]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.995178719095167</v>
+        <v>0.9747363320626209</v>
       </c>
       <c r="D10" t="n">
-        <v>0.995178719095167</v>
+        <v>0.9747363320626209</v>
       </c>
       <c r="E10" t="n">
-        <v>116.67</v>
+        <v>113.61</v>
       </c>
       <c r="F10" t="n">
-        <v>97.2</v>
+        <v>96.97</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[1, 5, 7, 4, 7]</t>
+          <t>[6, 9, 1, 6, 0]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9702662929835966</v>
+        <v>0.9618920412172819</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9702662929835966</v>
+        <v>0.9618920412172819</v>
       </c>
       <c r="E11" t="n">
-        <v>82.13</v>
+        <v>116.84</v>
       </c>
       <c r="F11" t="n">
-        <v>77.49999999999999</v>
+        <v>85.76000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[8, 2, 7, 3, 6]</t>
+          <t>[4, 0, 3, 5, 5]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 3]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9511760179783419</v>
+        <v>0.9697873041679935</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9511760179783419</v>
+        <v>0.9697873041679935</v>
       </c>
       <c r="E12" t="n">
-        <v>118.81</v>
+        <v>110.36</v>
       </c>
       <c r="F12" t="n">
-        <v>94.78</v>
+        <v>73.06</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[1, 5, 6, 2, 5]</t>
+          <t>[8, 7, 5, 2, 2]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9572425564070258</v>
+        <v>0.9727329973103529</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9572425564070258</v>
+        <v>0.9727329973103529</v>
       </c>
       <c r="E13" t="n">
-        <v>88.80000000000001</v>
+        <v>118.38</v>
       </c>
       <c r="F13" t="n">
-        <v>89.48999999999999</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[5, 1, 0, 0, 1]</t>
+          <t>[0, 2, 5, 0, 5]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.976211296920186</v>
+        <v>0.9793916941688572</v>
       </c>
       <c r="D14" t="n">
-        <v>0.976211296920186</v>
+        <v>0.9793916941688572</v>
       </c>
       <c r="E14" t="n">
-        <v>111.31</v>
+        <v>113</v>
       </c>
       <c r="F14" t="n">
-        <v>93.96000000000001</v>
+        <v>78.44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[4, 3, 4, 3, 7]</t>
+          <t>[7, 5, 7, 0, 3]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 3]</t>
+          <t>[2, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.975488630996128</v>
+        <v>0.9885114211539936</v>
       </c>
       <c r="D15" t="n">
-        <v>0.975488630996128</v>
+        <v>0.9885114211539936</v>
       </c>
       <c r="E15" t="n">
-        <v>118.95</v>
+        <v>119.87</v>
       </c>
       <c r="F15" t="n">
-        <v>95.14</v>
+        <v>99.03</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[8, 6, 0, 9, 5]</t>
+          <t>[7, 0, 6, 5, 5]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 3]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9482557296026123</v>
+        <v>0.9524355302010303</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9482557296026123</v>
+        <v>0.9524355302010303</v>
       </c>
       <c r="E16" t="n">
-        <v>104.01</v>
+        <v>113.36</v>
       </c>
       <c r="F16" t="n">
-        <v>88.29000000000001</v>
+        <v>84.56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[3, 0, 6, 5, 6]</t>
+          <t>[7, 5, 6, 8, 5]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9568966061632782</v>
+        <v>0.9644805629504511</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9568966061632782</v>
+        <v>0.9644805629504511</v>
       </c>
       <c r="E17" t="n">
-        <v>100.54</v>
+        <v>118.25</v>
       </c>
       <c r="F17" t="n">
-        <v>82.96000000000001</v>
+        <v>85.92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[0, 1, 4, 8, 3]</t>
+          <t>[9, 5, 8, 7, 8]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[2, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9718627159260915</v>
+        <v>0.9871546987953584</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9718627159260915</v>
+        <v>0.9871546987953584</v>
       </c>
       <c r="E18" t="n">
-        <v>109.52</v>
+        <v>109.59</v>
       </c>
       <c r="F18" t="n">
-        <v>83.36</v>
+        <v>97.73999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[0, 2, 2, 2, 5]</t>
+          <t>[7, 5, 1, 0, 8]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.958974455943257</v>
+        <v>0.9588161140012889</v>
       </c>
       <c r="D19" t="n">
-        <v>0.958974455943257</v>
+        <v>0.9588161140012889</v>
       </c>
       <c r="E19" t="n">
-        <v>95.49999999999999</v>
+        <v>96.41</v>
       </c>
       <c r="F19" t="n">
-        <v>81.5</v>
+        <v>82.70999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[4, 3, 7, 7, 1]</t>
+          <t>[7, 6, 7, 3, 1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[2, 1, 2, 1, 1]</t>
+          <t>[1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9747813814101193</v>
+        <v>0.9701316665260982</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9747813814101193</v>
+        <v>0.9701316665260982</v>
       </c>
       <c r="E20" t="n">
-        <v>102.95</v>
+        <v>116.87</v>
       </c>
       <c r="F20" t="n">
-        <v>87.57999999999998</v>
+        <v>98.45999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[0, 5, 5, 8, 7]</t>
+          <t>[8, 5, 3, 8, 8]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 2, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9722980247600485</v>
+        <v>0.9703398464371202</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9722980247600485</v>
+        <v>0.9703398464371202</v>
       </c>
       <c r="E21" t="n">
-        <v>92.89999999999999</v>
+        <v>109.93</v>
       </c>
       <c r="F21" t="n">
-        <v>85.23999999999999</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[3, 1, 2, 3, 6]</t>
+          <t>[8, 3, 6, 9, 3]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.993802357375809</v>
+        <v>0.935431756086618</v>
       </c>
       <c r="D22" t="n">
-        <v>0.993802357375809</v>
+        <v>0.935431756086618</v>
       </c>
       <c r="E22" t="n">
-        <v>119.01</v>
+        <v>97.31</v>
       </c>
       <c r="F22" t="n">
-        <v>97.46000000000001</v>
+        <v>67.47</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[7, 9, 3, 6, 8]</t>
+          <t>[3, 8, 5, 0, 8]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 2, 1, 2]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9672577106770969</v>
+        <v>0.97564572754575</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9672577106770969</v>
+        <v>0.97564572754575</v>
       </c>
       <c r="E23" t="n">
-        <v>101.24</v>
+        <v>115.62</v>
       </c>
       <c r="F23" t="n">
-        <v>79.69999999999999</v>
+        <v>88.76000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[7, 8, 5, 1, 1]</t>
+          <t>[8, 2, 9, 6, 9]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1000,22 +1000,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.951280432304638</v>
+        <v>0.942646037342759</v>
       </c>
       <c r="D24" t="n">
-        <v>0.951280432304638</v>
+        <v>0.942646037342759</v>
       </c>
       <c r="E24" t="n">
-        <v>91.3</v>
+        <v>112.56</v>
       </c>
       <c r="F24" t="n">
-        <v>86.44</v>
+        <v>88.57999999999998</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[4, 1, 4, 2, 7]</t>
+          <t>[5, 2, 9, 5, 7]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1024,310 +1024,310 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9731357200544124</v>
+        <v>0.960000884183123</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9731357200544124</v>
+        <v>0.960000884183123</v>
       </c>
       <c r="E25" t="n">
-        <v>102.82</v>
+        <v>99.48000000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>86.97</v>
+        <v>73.05000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[4, 1, 4, 3, 2]</t>
+          <t>[5, 6, 1, 7, 3]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[2, 2, 1, 1, 1]</t>
+          <t>[2, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9938627101148372</v>
+        <v>0.9880075805747195</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9938627101148372</v>
+        <v>0.9880075805747195</v>
       </c>
       <c r="E26" t="n">
-        <v>118.66</v>
+        <v>118.03</v>
       </c>
       <c r="F26" t="n">
-        <v>98.58</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[2, 3, 4, 1, 4]</t>
+          <t>[1, 7, 5, 1, 7]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 2]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9768135796034875</v>
+        <v>0.9556433530019323</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9768135796034875</v>
+        <v>0.9556433530019323</v>
       </c>
       <c r="E27" t="n">
-        <v>118.66</v>
+        <v>93.38000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>98.58</v>
+        <v>84.33</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[9, 7, 8, 4, 7]</t>
+          <t>[0, 3, 3, 7, 7]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9428786727386017</v>
+        <v>0.9681989290941619</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9428786727386017</v>
+        <v>0.9681989290941619</v>
       </c>
       <c r="E28" t="n">
-        <v>94.63000000000001</v>
+        <v>113.14</v>
       </c>
       <c r="F28" t="n">
-        <v>77.06</v>
+        <v>85.86000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[5, 4, 7, 7, 0]</t>
+          <t>[3, 7, 7, 8, 9]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 2]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9711330581376445</v>
+        <v>0.9636210691357562</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9711330581376445</v>
+        <v>0.9636210691357562</v>
       </c>
       <c r="E29" t="n">
-        <v>112.55</v>
+        <v>97.59</v>
       </c>
       <c r="F29" t="n">
-        <v>94.40000000000001</v>
+        <v>87.63999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[7, 3, 7, 7, 5]</t>
+          <t>[5, 1, 2, 4, 6]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 3]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.949293257290151</v>
+        <v>0.9560480406452402</v>
       </c>
       <c r="D30" t="n">
-        <v>0.949293257290151</v>
+        <v>0.9560480406452402</v>
       </c>
       <c r="E30" t="n">
-        <v>89.58000000000001</v>
+        <v>119.35</v>
       </c>
       <c r="F30" t="n">
-        <v>89.48</v>
+        <v>73.33</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[4, 3, 4, 6, 9]</t>
+          <t>[2, 0, 7, 2, 1]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9712813483430586</v>
+        <v>0.9786580729168406</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9712813483430586</v>
+        <v>0.9786580729168406</v>
       </c>
       <c r="E31" t="n">
-        <v>101.94</v>
+        <v>112.13</v>
       </c>
       <c r="F31" t="n">
-        <v>78.2</v>
+        <v>79.52</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[5, 2, 2, 1, 2]</t>
+          <t>[5, 5, 7, 8, 8]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9760758909875676</v>
+        <v>0.9683018551575325</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9760758909875676</v>
+        <v>0.9683018551575325</v>
       </c>
       <c r="E32" t="n">
-        <v>100.19</v>
+        <v>102.08</v>
       </c>
       <c r="F32" t="n">
-        <v>95.28</v>
+        <v>85.81999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[4, 1, 8, 6, 5]</t>
+          <t>[8, 0, 7, 8, 4]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 2, 1]</t>
+          <t>[2, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.989543772470288</v>
+        <v>0.9784551174450328</v>
       </c>
       <c r="D33" t="n">
-        <v>0.989543772470288</v>
+        <v>0.9784551174450328</v>
       </c>
       <c r="E33" t="n">
-        <v>116.52</v>
+        <v>116.06</v>
       </c>
       <c r="F33" t="n">
-        <v>97.34999999999999</v>
+        <v>99.88</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[7, 2, 4, 4, 6]</t>
+          <t>[7, 1, 8, 5, 0]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[2, 1, 2, 1, 1]</t>
+          <t>[1, 3, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9780314384585858</v>
+        <v>0.9663364891233311</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9780314384585858</v>
+        <v>0.9663364891233311</v>
       </c>
       <c r="E34" t="n">
-        <v>113.87</v>
+        <v>118.03</v>
       </c>
       <c r="F34" t="n">
-        <v>92.72</v>
+        <v>98.86</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[6, 8, 5, 6, 2]</t>
+          <t>[8, 8, 6, 2, 4]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9669134136785942</v>
+        <v>0.9669631031549792</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9669134136785942</v>
+        <v>0.9669631031549792</v>
       </c>
       <c r="E35" t="n">
-        <v>103.07</v>
+        <v>115.68</v>
       </c>
       <c r="F35" t="n">
-        <v>86.28</v>
+        <v>74.97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[3, 0, 8, 3, 2]</t>
+          <t>[8, 9, 8, 2, 7]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 2, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9563651097174111</v>
+        <v>0.9854975942088396</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9563651097174111</v>
+        <v>0.9854975942088396</v>
       </c>
       <c r="E36" t="n">
-        <v>115.23</v>
+        <v>117.44</v>
       </c>
       <c r="F36" t="n">
-        <v>87.15000000000001</v>
+        <v>99.95999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[6, 3, 2, 7, 0]</t>
+          <t>[6, 4, 5, 3, 7]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9701172093845616</v>
+        <v>0.9631535541863017</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9701172093845616</v>
+        <v>0.9631535541863017</v>
       </c>
       <c r="E37" t="n">
-        <v>107.71</v>
+        <v>118.55</v>
       </c>
       <c r="F37" t="n">
-        <v>86.65000000000001</v>
+        <v>77.58</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[3, 5, 9, 1, 2]</t>
+          <t>[2, 8, 9, 6, 5]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1336,46 +1336,46 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9722143679015732</v>
+        <v>0.961280379172915</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9722143679015732</v>
+        <v>0.961280379172915</v>
       </c>
       <c r="E38" t="n">
-        <v>98.08</v>
+        <v>113.2</v>
       </c>
       <c r="F38" t="n">
-        <v>85.37</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[7, 4, 9, 8, 4]</t>
+          <t>[5, 2, 8, 4, 6]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9435213996375686</v>
+        <v>0.9627634649539375</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9435213996375686</v>
+        <v>0.9627634649539375</v>
       </c>
       <c r="E39" t="n">
-        <v>104.79</v>
+        <v>118.54</v>
       </c>
       <c r="F39" t="n">
-        <v>80.22</v>
+        <v>69.05</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[2, 9, 1, 7, 3]</t>
+          <t>[9, 1, 1, 9, 5]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1384,280 +1384,280 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.963858071689335</v>
+        <v>0.9684776404834119</v>
       </c>
       <c r="D40" t="n">
-        <v>0.963858071689335</v>
+        <v>0.9684776404834119</v>
       </c>
       <c r="E40" t="n">
-        <v>102.69</v>
+        <v>106.16</v>
       </c>
       <c r="F40" t="n">
-        <v>87.78999999999999</v>
+        <v>93.18000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[3, 3, 7, 1, 8]</t>
+          <t>[8, 2, 9, 1, 5]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 2]</t>
+          <t>[1, 1, 1, 1, 3]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9771394723039037</v>
+        <v>0.949442070199338</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9771394723039037</v>
+        <v>0.949442070199338</v>
       </c>
       <c r="E41" t="n">
-        <v>113.02</v>
+        <v>118.01</v>
       </c>
       <c r="F41" t="n">
-        <v>89.59999999999999</v>
+        <v>86.31</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[8, 3, 1, 8, 1]</t>
+          <t>[8, 0, 0, 5, 7]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[1, 2, 2, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9896247166768499</v>
+        <v>0.9751012179828663</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9896247166768499</v>
+        <v>0.9751012179828663</v>
       </c>
       <c r="E42" t="n">
-        <v>118.78</v>
+        <v>98.73000000000002</v>
       </c>
       <c r="F42" t="n">
-        <v>97.54000000000002</v>
+        <v>81.03</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[6, 5, 2, 1, 0]</t>
+          <t>[5, 8, 7, 8, 5]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 3]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9722489788757419</v>
+        <v>0.9650666845231906</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9722489788757419</v>
+        <v>0.9650666845231906</v>
       </c>
       <c r="E43" t="n">
-        <v>99.37</v>
+        <v>116.81</v>
       </c>
       <c r="F43" t="n">
-        <v>91.17000000000002</v>
+        <v>96.13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[9, 3, 5, 0, 7]</t>
+          <t>[2, 3, 1, 0, 7]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 3]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9529471473204096</v>
+        <v>0.9785431350689545</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9529471473204096</v>
+        <v>0.9785431350689545</v>
       </c>
       <c r="E44" t="n">
-        <v>107.04</v>
+        <v>115.5</v>
       </c>
       <c r="F44" t="n">
-        <v>92.11</v>
+        <v>81.92</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[9, 5, 0, 7, 3]</t>
+          <t>[2, 5, 3, 8, 2]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[1, 2, 2, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9886672968308032</v>
+        <v>0.9634945649752951</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9886672968308032</v>
+        <v>0.9634945649752951</v>
       </c>
       <c r="E45" t="n">
-        <v>117.39</v>
+        <v>119.07</v>
       </c>
       <c r="F45" t="n">
-        <v>99.81</v>
+        <v>66.60000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[1, 9, 3, 0, 0]</t>
+          <t>[5, 6, 4, 0, 9]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.971446890279399</v>
+        <v>0.9667762421792473</v>
       </c>
       <c r="D46" t="n">
-        <v>0.971446890279399</v>
+        <v>0.9667762421792473</v>
       </c>
       <c r="E46" t="n">
-        <v>110.99</v>
+        <v>117.45</v>
       </c>
       <c r="F46" t="n">
-        <v>90.24000000000001</v>
+        <v>86.72999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[9, 9, 3, 2, 7]</t>
+          <t>[7, 4, 2, 1, 0]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.9665617438695038</v>
+        <v>0.9735355712022099</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9665617438695038</v>
+        <v>0.9735355712022099</v>
       </c>
       <c r="E47" t="n">
-        <v>102.09</v>
+        <v>113.15</v>
       </c>
       <c r="F47" t="n">
-        <v>82.34999999999999</v>
+        <v>84.07000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[4, 9, 5, 7, 2]</t>
+          <t>[4, 9, 0, 7, 5]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9875896347797093</v>
+        <v>0.9738495141551741</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9875896347797093</v>
+        <v>0.9738495141551741</v>
       </c>
       <c r="E48" t="n">
-        <v>111.24</v>
+        <v>105.46</v>
       </c>
       <c r="F48" t="n">
-        <v>96.01000000000001</v>
+        <v>87.93000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[8, 9, 0, 1, 3]</t>
+          <t>[5, 5, 6, 0, 8]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[3, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.9541221010422146</v>
+        <v>0.9759389846240492</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9541221010422146</v>
+        <v>0.9759389846240492</v>
       </c>
       <c r="E49" t="n">
-        <v>109.39</v>
+        <v>113.79</v>
       </c>
       <c r="F49" t="n">
-        <v>84.18000000000001</v>
+        <v>83.06999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[6, 1, 7, 9, 2]</t>
+          <t>[9, 5, 3, 0, 5]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.9720483414109085</v>
+        <v>0.9646526280439481</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9720483414109085</v>
+        <v>0.9646526280439481</v>
       </c>
       <c r="E50" t="n">
-        <v>108.29</v>
+        <v>105.02</v>
       </c>
       <c r="F50" t="n">
-        <v>95.91</v>
+        <v>76.81</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[6, 7, 6, 6, 8]</t>
+          <t>[2, 8, 5, 1, 6]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.9664081607203033</v>
+        <v>0.9485374001609427</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9664081607203033</v>
+        <v>0.9485374001609427</v>
       </c>
       <c r="E51" t="n">
-        <v>95.43000000000001</v>
+        <v>90.16000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>77.81999999999999</v>
+        <v>60.27</v>
       </c>
     </row>
   </sheetData>
